--- a/src/attributions/attributions_saliency_traj_408.xlsx
+++ b/src/attributions/attributions_saliency_traj_408.xlsx
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01190735399723053</v>
+        <v>0.4075919985771179</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3488459587097168</v>
+        <v>0.2566432952880859</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03446622937917709</v>
+        <v>0.1937083303928375</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1044684052467346</v>
+        <v>0.1959008872509003</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1950882375240326</v>
+        <v>0.08445674180984497</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2376260310411453</v>
+        <v>0.266085684299469</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3216951489448547</v>
+        <v>0.1868387162685394</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03232410922646523</v>
+        <v>0.01599461585283279</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3695054948329926</v>
+        <v>0.1322011500597</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1152338460087776</v>
+        <v>0.3667940497398376</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1567512452602386</v>
+        <v>0.4995209872722626</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08804047107696533</v>
+        <v>0.1164539456367493</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2570171356201172</v>
+        <v>0.5446724891662598</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4800397157669067</v>
+        <v>0.3509235978126526</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2833370566368103</v>
+        <v>0.3593790531158447</v>
       </c>
       <c r="P2" t="n">
-        <v>0.03734236210584641</v>
+        <v>0.1640544235706329</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2144326269626617</v>
+        <v>0.2358841896057129</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2747200131416321</v>
+        <v>0.02522888407111168</v>
       </c>
       <c r="S2" t="n">
-        <v>0.008618599735200405</v>
+        <v>0.05821497365832329</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1222328245639801</v>
+        <v>0.01167673338204622</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01766063272953033</v>
+        <v>0.07974447309970856</v>
       </c>
       <c r="V2" t="n">
-        <v>0.08420941978693008</v>
+        <v>0.02908847108483315</v>
       </c>
       <c r="W2" t="n">
-        <v>0.04666256904602051</v>
+        <v>0.03758560866117477</v>
       </c>
       <c r="X2" t="n">
-        <v>0.04028850421309471</v>
+        <v>0.08273828029632568</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.06083012372255325</v>
+        <v>0.02535346895456314</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.064788818359375</v>
+        <v>0.05853134766221046</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01475559920072556</v>
+        <v>0.1027994900941849</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.09175475686788559</v>
+        <v>0.02531184256076813</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.2294254899024963</v>
+        <v>0.005463495850563049</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.03292171284556389</v>
+        <v>0.06963019073009491</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.01674710214138031</v>
+        <v>0.2505225539207458</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2663972973823547</v>
+        <v>0.01799312420189381</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.08760030567646027</v>
+        <v>0.1702937334775925</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.02325086668133736</v>
+        <v>0.0497402735054493</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.01113741844892502</v>
+        <v>0.01567436195909977</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.01369318924844265</v>
+        <v>0.072801873087883</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.01924444735050201</v>
+        <v>0.08420903980731964</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.03291217610239983</v>
+        <v>0.06006534397602081</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.007591260597109795</v>
+        <v>0.1017906665802002</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.03453382104635239</v>
+        <v>0.04286853969097137</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.05631418898701668</v>
+        <v>0.1465093195438385</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.08369661122560501</v>
+        <v>0.1159587278962135</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.02873104996979237</v>
+        <v>0.05118130892515182</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.1811885833740234</v>
+        <v>0.00530301034450531</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.00908850971609354</v>
+        <v>0.0199924036860466</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.04979965090751648</v>
+        <v>0.0570649579167366</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.1559393256902695</v>
+        <v>0.09076639264822006</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.05534665286540985</v>
+        <v>0.09293670952320099</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.01440198719501495</v>
+        <v>0.4067848920822144</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.01231607981026173</v>
+        <v>0.2997099459171295</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.2149161100387573</v>
+        <v>0.1422703862190247</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.07825049757957458</v>
+        <v>0.01800025440752506</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.1877017915248871</v>
+        <v>0.0340832993388176</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.1794038414955139</v>
+        <v>0.06951208412647247</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.05291172116994858</v>
+        <v>0.1859232932329178</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.009551368653774261</v>
+        <v>0.0345638170838356</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.06815171986818314</v>
+        <v>0.04284892603754997</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.142340749502182</v>
+        <v>0.176064133644104</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.229450985789299</v>
+        <v>0.06361780315637589</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.02877992577850819</v>
+        <v>0.1195129305124283</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.1360237151384354</v>
+        <v>0.04316956549882889</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.2052839994430542</v>
+        <v>0.0327986404299736</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.02785542234778404</v>
+        <v>0.2545114457607269</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.04993285611271858</v>
+        <v>0.1445872336626053</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.01347708143293858</v>
+        <v>0.03877478465437889</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.01218343898653984</v>
+        <v>0.03318927064538002</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.1380428820848465</v>
+        <v>0.0009478181600570679</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.07305559515953064</v>
+        <v>0.07007109373807907</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.05378930270671844</v>
+        <v>0.01587601564824581</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.2209028154611588</v>
+        <v>0.0519961379468441</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.1175228431820869</v>
+        <v>0.05830850452184677</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.00516776368021965</v>
+        <v>0.006666442379355431</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.01513251196593046</v>
+        <v>0.01878340914845467</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.112921766936779</v>
+        <v>0.1403380483388901</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.05084577947854996</v>
+        <v>0.1410604864358902</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.008857950568199158</v>
+        <v>0.2694581747055054</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.1112204641103745</v>
+        <v>0.05799493938684464</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.1047546342015266</v>
+        <v>0.09817312657833099</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.03243328630924225</v>
+        <v>0.0925476923584938</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.150716558098793</v>
+        <v>0.003171521704643965</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.09562236070632935</v>
+        <v>0.07344133406877518</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.01087179966270924</v>
+        <v>0.06094885617494583</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.08644524216651917</v>
+        <v>0.08876758813858032</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.01595222391188145</v>
+        <v>0.009082288481295109</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.01393509469926357</v>
+        <v>0.09490638971328735</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01033997535705566</v>
+        <v>0.005374103784561157</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.01955493539571762</v>
+        <v>0.002648189663887024</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.03410709649324417</v>
+        <v>0.006411001086235046</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.02193360403180122</v>
+        <v>0.02136128023266792</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.07331828773021698</v>
+        <v>0.06198764219880104</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.03765731304883957</v>
+        <v>0.08968669921159744</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.08038299530744553</v>
+        <v>0.2028226256370544</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.0464308001101017</v>
+        <v>0.03761246055364609</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.05009744688868523</v>
+        <v>0.3607158958911896</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.01848739944398403</v>
+        <v>0.1859766095876694</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.007035217247903347</v>
+        <v>0.0343702919781208</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.04218287020921707</v>
+        <v>0.02827884256839752</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.01408366020768881</v>
+        <v>0.08247603476047516</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.06618814915418625</v>
+        <v>0.1552912443876266</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.01869319006800652</v>
+        <v>0.03283696249127388</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.08608897030353546</v>
+        <v>0.099831722676754</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.01318404264748096</v>
+        <v>0.03217095136642456</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.04896844178438187</v>
+        <v>0.1160554811358452</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.02650985866785049</v>
+        <v>0.05784473940730095</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.02274208329617977</v>
+        <v>0.004424655809998512</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.02364440262317657</v>
+        <v>0.009942579083144665</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.03098712116479874</v>
+        <v>0.0102099422365427</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.07885004580020905</v>
+        <v>0.06768635660409927</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.04147079214453697</v>
+        <v>0.03062332421541214</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.1532569825649261</v>
+        <v>0.5728758573532104</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.04912613332271576</v>
+        <v>0.02021390572190285</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.04714648425579071</v>
+        <v>0.0509544312953949</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.4100653529167175</v>
+        <v>0.01621728762984276</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.07869285345077515</v>
+        <v>0.2451341301202774</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.2179968059062958</v>
+        <v>0.05145547538995743</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.01453462988138199</v>
+        <v>0.2293321937322617</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.08478544652462006</v>
+        <v>0.03476659208536148</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.03489373624324799</v>
+        <v>0.005373751744627953</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.002997148782014847</v>
+        <v>0.04029084369540215</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.1116348952054977</v>
+        <v>0.03990034013986588</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.09604014456272125</v>
+        <v>0.007910728454589844</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.06635375320911407</v>
+        <v>0.1235616356134415</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.06533297151327133</v>
+        <v>0.02564996108412743</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.09140722453594208</v>
+        <v>0.09153525531291962</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.08869897574186325</v>
+        <v>0.04976428672671318</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.103577733039856</v>
+        <v>0.1665345281362534</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.01409260369837284</v>
+        <v>0.004763294942677021</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.09421345591545105</v>
+        <v>0.120543859899044</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.09347048401832581</v>
+        <v>0.2269809395074844</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.03306389600038528</v>
+        <v>0.0502421110868454</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.0524568110704422</v>
+        <v>0.108689546585083</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.08141627162694931</v>
+        <v>0.08379827439785004</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.05683377757668495</v>
+        <v>0.02551229111850262</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.1047883182764053</v>
+        <v>0.2204800546169281</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.09233859181404114</v>
+        <v>0.2126873731613159</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.03618938103318214</v>
+        <v>0.043871209025383</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.00167064368724823</v>
+        <v>0.009218920022249222</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.01442330982536077</v>
+        <v>0.02907678671181202</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.1789011210203171</v>
+        <v>0.06934738904237747</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.1668380200862885</v>
+        <v>0.05015430599451065</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.03357473760843277</v>
+        <v>0.01555688958615065</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.07964406162500381</v>
+        <v>0.01904527842998505</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.0512201339006424</v>
+        <v>0.03802608698606491</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.03514337912201881</v>
+        <v>0.05439886450767517</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.03626089915633202</v>
+        <v>0.03906022012233734</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.06169478595256805</v>
+        <v>0.100097194314003</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.005661085713654757</v>
+        <v>0.04834647476673126</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.1109533756971359</v>
+        <v>0.02735428512096405</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.007327089086174965</v>
+        <v>0.04712818935513496</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.03036436066031456</v>
+        <v>0.2627552151679993</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.09485419094562531</v>
+        <v>0.1001567393541336</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.07425947487354279</v>
+        <v>0.04821781814098358</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.04048393666744232</v>
+        <v>0.09011708199977875</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.04717907682061195</v>
+        <v>0.04138829186558723</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.09421554207801819</v>
+        <v>0.1545735746622086</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.008209727704524994</v>
+        <v>0.03087978065013885</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.05515792965888977</v>
+        <v>0.1099980100989342</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.009587079286575317</v>
+        <v>0.04775989055633545</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.06169139593839645</v>
+        <v>0.01091394387185574</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.07816561311483383</v>
+        <v>0.02301496267318726</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.01158355455845594</v>
+        <v>0.03213834390044212</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.04802072048187256</v>
+        <v>0.06362909078598022</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.05109360069036484</v>
+        <v>0.115061990916729</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.06186333298683167</v>
+        <v>0.09527587890625</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.002200838178396225</v>
+        <v>0.1280232816934586</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.006861470639705658</v>
+        <v>0.09523056447505951</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.03615248203277588</v>
+        <v>0.1403572261333466</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.01966219767928123</v>
+        <v>0.1959752142429352</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.0549294576048851</v>
+        <v>0.005030754953622818</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.1125282496213913</v>
+        <v>0.02692942880094051</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.04796082526445389</v>
+        <v>0.08963146060705185</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.01067672111093998</v>
+        <v>0.06859403848648071</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.05317968502640724</v>
+        <v>0.1137169599533081</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.01151658594608307</v>
+        <v>0.1830613017082214</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.1161595731973648</v>
+        <v>0.01828917115926743</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.2447248101234436</v>
+        <v>0.3136678338050842</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.2047241181135178</v>
+        <v>0.07974929362535477</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.08762088418006897</v>
+        <v>0.051241435110569</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.07608505338430405</v>
+        <v>0.04718049615621567</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.04518121480941772</v>
+        <v>0.1042773947119713</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.04422522336244583</v>
+        <v>0.1632026731967926</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.01852928102016449</v>
+        <v>0.06878800690174103</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.02832689508795738</v>
+        <v>0.01368077099323273</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.07055473327636719</v>
+        <v>0.05251090228557587</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.05726753547787666</v>
+        <v>0.1031379327178001</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.06220478937029839</v>
+        <v>0.03729448467493057</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.1138705983757973</v>
+        <v>0.1726986765861511</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.1390234231948853</v>
+        <v>0.07522521913051605</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.1597185432910919</v>
+        <v>0.00343936774879694</v>
       </c>
     </row>
     <row r="3">
@@ -2137,5123 +2137,5123 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.1620070189237595</v>
+        <v>0.003377554006874561</v>
       </c>
       <c r="B4" t="n">
-        <v>3.762916803359985</v>
+        <v>0.04192394390702248</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2214437127113342</v>
+        <v>0.005181291606277227</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7831493020057678</v>
+        <v>0.02333215996623039</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4010783433914185</v>
+        <v>0.01677982322871685</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2611935436725616</v>
+        <v>0.02780472859740257</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2203761041164398</v>
+        <v>0.007662471383810043</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8780397772789001</v>
+        <v>0.003374180756509304</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003458131104707718</v>
+        <v>0.005071492400020361</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4590705335140228</v>
+        <v>5.485373549163342e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.086766958236694</v>
+        <v>0.03995361179113388</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1347094029188156</v>
+        <v>0.0006318832747638226</v>
       </c>
       <c r="M4" t="n">
-        <v>1.639392971992493</v>
+        <v>0.03195973485708237</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1276790201663971</v>
+        <v>0.02399392798542976</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6177434325218201</v>
+        <v>0.02833998203277588</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0668046846985817</v>
+        <v>0.0148041695356369</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5993844866752625</v>
+        <v>0.003821825608611107</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2091891467571259</v>
+        <v>0.001704102847725153</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05496717616915703</v>
+        <v>0.002466003410518169</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7449548244476318</v>
+        <v>0.004212499596178532</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003942172974348068</v>
+        <v>0.004546178970485926</v>
       </c>
       <c r="V4" t="n">
-        <v>0.242769330739975</v>
+        <v>0.002300705295056105</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7599284052848816</v>
+        <v>0.00128913507796824</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5124219655990601</v>
+        <v>0.01201298087835312</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09751652181148529</v>
+        <v>0.002021111315116286</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.005675312131643295</v>
+        <v>0.003265034174546599</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2538590133190155</v>
+        <v>0.00395121518522501</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.210442066192627</v>
+        <v>0.002772071398794651</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7423786520957947</v>
+        <v>0.003455952741205692</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1835835427045822</v>
+        <v>0.001732504344545305</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.04288995265960693</v>
+        <v>0.008289117366075516</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1171429753303528</v>
+        <v>0.0003245202824473381</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.4627545475959778</v>
+        <v>0.002622164785861969</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.6521517038345337</v>
+        <v>0.0006125998916104436</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.261402040719986</v>
+        <v>0.005518014077097178</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.2544838786125183</v>
+        <v>0.003243978833779693</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.2861990332603455</v>
+        <v>0.001922702183946967</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.1166533604264259</v>
+        <v>0.007712168619036674</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.1313349157571793</v>
+        <v>0.002393194241449237</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.3328830301761627</v>
+        <v>0.004339909180998802</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.1528265774250031</v>
+        <v>0.00384236266836524</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.08456439524888992</v>
+        <v>0.004949813243001699</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.1883654594421387</v>
+        <v>0.003863200545310974</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.1320786625146866</v>
+        <v>0.003050628118216991</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.02067116647958755</v>
+        <v>0.0006152872228994966</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.01307011302560568</v>
+        <v>0.003008609171956778</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.197206735610962</v>
+        <v>0.01564224064350128</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.5691629648208618</v>
+        <v>0.005190588533878326</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.09513527154922485</v>
+        <v>0.01559418812394142</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.681023240089417</v>
+        <v>0.02909164689481258</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.2233370989561081</v>
+        <v>0.01088973507285118</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1066100001335144</v>
+        <v>0.005042625591158867</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.6916866898536682</v>
+        <v>0.003222013125196099</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.2534460723400116</v>
+        <v>0.0008305972442030907</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.5001698732376099</v>
+        <v>0.0106054712086916</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.639136791229248</v>
+        <v>0.01424247585237026</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.5723777413368225</v>
+        <v>0.003359136171638966</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.09944753348827362</v>
+        <v>0.003620933974161744</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.9666901826858521</v>
+        <v>0.004871482960879803</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.1505236476659775</v>
+        <v>0.01216375362128019</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.2212389409542084</v>
+        <v>0.002026967005804181</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0499262847006321</v>
+        <v>0.004914947785437107</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.3865130841732025</v>
+        <v>0.006223408505320549</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.3901576995849609</v>
+        <v>0.001999357482418418</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.3833950757980347</v>
+        <v>0.002624668646603823</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.04773144423961639</v>
+        <v>0.0002618246653582901</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.799907922744751</v>
+        <v>0.001009909901767969</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.7753860354423523</v>
+        <v>0.006436815019696951</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.5082931518554688</v>
+        <v>0.001463458407670259</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.4275272190570831</v>
+        <v>0.001538962009362876</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.1603851765394211</v>
+        <v>0.003540717530995607</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.7328736186027527</v>
+        <v>0.001297365641221404</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.1397398263216019</v>
+        <v>0.001877440838143229</v>
       </c>
       <c r="BV4" t="n">
-        <v>1.297323942184448</v>
+        <v>0.0119703896343708</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.3686472177505493</v>
+        <v>0.0003185502719134092</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.2849477231502533</v>
+        <v>0.01144501660019159</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.7274776101112366</v>
+        <v>0.009324481710791588</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.03450636565685272</v>
+        <v>0.0106955049559474</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.2175848931074142</v>
+        <v>0.004709637258201838</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.2796549797058105</v>
+        <v>0.002606083871796727</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.1630615741014481</v>
+        <v>0.0002109918277710676</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.088971763849258e-05</v>
+        <v>0.0005701510235667229</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.7468045353889465</v>
+        <v>0.01094797998666763</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.0636548176407814</v>
+        <v>0.002993527799844742</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.02555029839277267</v>
+        <v>0.008186913095414639</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.1236432790756226</v>
+        <v>0.003700085449963808</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0136375455185771</v>
+        <v>0.001827871892601252</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.1717660427093506</v>
+        <v>0.001209280220791698</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.06939281523227692</v>
+        <v>0.00252135843038559</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.05420831963419914</v>
+        <v>7.288293272722512e-05</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.7362917065620422</v>
+        <v>0.004956784192472696</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.3390935957431793</v>
+        <v>0.009851147420704365</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.2007688283920288</v>
+        <v>0.01257425174117088</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.016264677047729</v>
+        <v>0.01260954141616821</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.7976371645927429</v>
+        <v>0.004747865721583366</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.139946460723877</v>
+        <v>0.0009459196007810533</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.2143821716308594</v>
+        <v>0.0005328244296833873</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.06978227943181992</v>
+        <v>0.008128268644213676</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.1677250564098358</v>
+        <v>0.0006053636316210032</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.007824050262570381</v>
+        <v>0.0003524824278429151</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.6828275322914124</v>
+        <v>0.01118609122931957</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.2280623912811279</v>
+        <v>0.002605269197374582</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.1210202053189278</v>
+        <v>0.009197583422064781</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.2840490341186523</v>
+        <v>0.003604500088840723</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0008313045836985111</v>
+        <v>0.002268189564347267</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.175937682390213</v>
+        <v>0.00193255627527833</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.06684628129005432</v>
+        <v>0.001799921039491892</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.04676886275410652</v>
+        <v>0.001405292772687972</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.4724210500717163</v>
+        <v>0.008336346596479416</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.5389456748962402</v>
+        <v>0.02308753319084644</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.1175742745399475</v>
+        <v>0.002294423989951611</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.4882186949253082</v>
+        <v>0.01425194088369608</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.3456313014030457</v>
+        <v>0.002556533552706242</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.2766629755496979</v>
+        <v>0.006823801901191473</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.2048331201076508</v>
+        <v>0.001380289089865983</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.01830191165208817</v>
+        <v>0.008282242342829704</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.1105072945356369</v>
+        <v>0.00223732041195035</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.3037740588188171</v>
+        <v>0.002509318292140961</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.6432312726974487</v>
+        <v>0.005235172342509031</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.3374030292034149</v>
+        <v>0.004719413816928864</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.8477404117584229</v>
+        <v>0.002406737534329295</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.305814802646637</v>
+        <v>0.006688868626952171</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.199366420507431</v>
+        <v>0.001111952587962151</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.1979236304759979</v>
+        <v>0.004091054666787386</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.06747380644083023</v>
+        <v>0.004131269175559282</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.7065526843070984</v>
+        <v>0.005161753855645657</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.001138556748628616</v>
+        <v>0.003963912837207317</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.157924696803093</v>
+        <v>0.0009691164596006274</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.02821560204029083</v>
+        <v>0.0001754678087309003</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.3103061318397522</v>
+        <v>0.009120042435824871</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.07710106670856476</v>
+        <v>0.001435545622371137</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.1111257374286652</v>
+        <v>7.067450496833771e-05</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.0003032498061656952</v>
+        <v>0.0001192573690786958</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.3554878830909729</v>
+        <v>0.01438187155872583</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.1760763823986053</v>
+        <v>0.006199360825121403</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.08031053096055984</v>
+        <v>0.006199168972671032</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.4176374673843384</v>
+        <v>0.0104868970811367</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.2654496133327484</v>
+        <v>0.003288660431280732</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.03229328989982605</v>
+        <v>0.005073863081634045</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.1796676963567734</v>
+        <v>0.00145810644607991</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.1816015392541885</v>
+        <v>0.0004165545105934143</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.1956726163625717</v>
+        <v>0.00154176726937294</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.08919281512498856</v>
+        <v>0.002303802641108632</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.01161040738224983</v>
+        <v>0.001698422245681286</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.0305112898349762</v>
+        <v>0.001702888403087854</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.4712948799133301</v>
+        <v>0.007976975291967392</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.4054784774780273</v>
+        <v>0.00588576914742589</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.9369372129440308</v>
+        <v>0.001029512146487832</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.6080719828605652</v>
+        <v>0.003879309631884098</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.4531510174274445</v>
+        <v>0.0001905873068608344</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.1240212023258209</v>
+        <v>0.005630054511129856</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.385138601064682</v>
+        <v>0.004764324985444546</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.146138072013855</v>
+        <v>0.004981116857379675</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.1054975688457489</v>
+        <v>0.001091685495339334</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.736358106136322</v>
+        <v>0.01140245050191879</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.04661235213279724</v>
+        <v>0.001923466101288795</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.04362296313047409</v>
+        <v>0.01042147353291512</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.2156704515218735</v>
+        <v>0.002641361905261874</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.07409423589706421</v>
+        <v>0.001412468729540706</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.1413934677839279</v>
+        <v>0.002001439686864614</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.09035372734069824</v>
+        <v>0.003674827516078949</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.07036690413951874</v>
+        <v>0.001547202235087752</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.1282343566417694</v>
+        <v>0.003693314734846354</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.1442175805568695</v>
+        <v>0.006830170750617981</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.4384155571460724</v>
+        <v>0.004489797167479992</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.2217673510313034</v>
+        <v>0.008998382836580276</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.4129590690135956</v>
+        <v>0.003850063541904092</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.2691710293292999</v>
+        <v>0.006523394957184792</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.06788569688796997</v>
+        <v>0.0005052234046161175</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.01470822095870972</v>
+        <v>0.00538945896551013</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.6036493182182312</v>
+        <v>0.0009886051993817091</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.4328391849994659</v>
+        <v>0.007618427742272615</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.05753817409276962</v>
+        <v>0.005010586231946945</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.4470478892326355</v>
+        <v>0.0006407769396901131</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.2029913663864136</v>
+        <v>0.01759245805442333</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.006364285945892334</v>
+        <v>0.02888267114758492</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.304003894329071</v>
+        <v>0.004487436264753342</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.5502414703369141</v>
+        <v>0.001857339288108051</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.6821551322937012</v>
+        <v>0.006995499134063721</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.3723915219306946</v>
+        <v>0.009014295414090157</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.4601988196372986</v>
+        <v>0.008704285137355328</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.1186534464359283</v>
+        <v>0.006722593680024147</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.1237955465912819</v>
+        <v>0.008977431803941727</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.2754144668579102</v>
+        <v>0.003319099079817533</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.04801421612501144</v>
+        <v>0.006169060245156288</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.7095024585723877</v>
+        <v>0.006766875274479389</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.5338696241378784</v>
+        <v>0.006218795198947191</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.1243206933140755</v>
+        <v>0.0004584149573929608</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.1876660585403442</v>
+        <v>0.0005907501908950508</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.5419383645057678</v>
+        <v>0.05732695758342743</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6243898868560791</v>
+        <v>0.09748397022485733</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03574038296937943</v>
+        <v>0.02334490418434143</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06997410207986832</v>
+        <v>0.005210652947425842</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004989132285118103</v>
+        <v>0.03157802298665047</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1425807029008865</v>
+        <v>0.02678842656314373</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3413940072059631</v>
+        <v>0.008123628795146942</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1315355151891708</v>
+        <v>0.01004092954099178</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005553700961172581</v>
+        <v>0.01467173546552658</v>
       </c>
       <c r="J5" t="n">
-        <v>0.314675897359848</v>
+        <v>0.05494819208979607</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5754919052124023</v>
+        <v>0.1170795112848282</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04167283326387405</v>
+        <v>0.03039175644516945</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2709552049636841</v>
+        <v>0.007525421213358641</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2368346750736237</v>
+        <v>0.05733129009604454</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1446159482002258</v>
+        <v>0.011640515178442</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1531666219234467</v>
+        <v>0.01903074979782104</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.341131329536438</v>
+        <v>0.003908771555870771</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2715663909912109</v>
+        <v>0.03355978801846504</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03951560705900192</v>
+        <v>0.002902108244597912</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2455053627490997</v>
+        <v>0.005122872535139322</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09178676456212997</v>
+        <v>0.00856506172567606</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3014127016067505</v>
+        <v>0.00499620009213686</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1415542215108871</v>
+        <v>0.00478803738951683</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1011804193258286</v>
+        <v>0.0007134489715099335</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2543491721153259</v>
+        <v>0.003849411383271217</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1734184175729752</v>
+        <v>0.01944445446133614</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0770379900932312</v>
+        <v>0.01060258597135544</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2659924328327179</v>
+        <v>0.00643252395093441</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.2570560574531555</v>
+        <v>0.007271150127053261</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.07309751957654953</v>
+        <v>0.01457571052014828</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.01587646454572678</v>
+        <v>0.01622244715690613</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3114397525787354</v>
+        <v>0.001876242458820343</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.1427644789218903</v>
+        <v>0.01129126083105803</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.3929570317268372</v>
+        <v>0.01210019178688526</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.06528886407613754</v>
+        <v>0.0005993307568132877</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.1634650081396103</v>
+        <v>0.004969292785972357</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1082360744476318</v>
+        <v>0.01308081671595573</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.1914803087711334</v>
+        <v>0.02937610819935799</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.03231505677103996</v>
+        <v>0.008109349757432938</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.05098620802164078</v>
+        <v>0.002999785589054227</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.257232129573822</v>
+        <v>0.009497277438640594</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.07918782532215118</v>
+        <v>0.01202654466032982</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0416901595890522</v>
+        <v>0.00774946017190814</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.03509893640875816</v>
+        <v>3.466929774731398e-05</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.04205165058374405</v>
+        <v>0.001420977059751749</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0258149765431881</v>
+        <v>0.0301548670977354</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3750711679458618</v>
+        <v>0.04628384113311768</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.1078360229730606</v>
+        <v>0.01081006042659283</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1243695095181465</v>
+        <v>0.003473582211881876</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.3504052758216858</v>
+        <v>0.02549037896096706</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.001638278365135193</v>
+        <v>0.002295134589076042</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1448125243186951</v>
+        <v>0.003603791352361441</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.1483479142189026</v>
+        <v>0.01243449095636606</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.1844871640205383</v>
+        <v>0.003350915387272835</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.1199553906917572</v>
+        <v>0.01273946277797222</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0117451511323452</v>
+        <v>0.02539564296603203</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.06290213018655777</v>
+        <v>0.02936066128313541</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.09295978397130966</v>
+        <v>0.003570747561752796</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.3045215606689453</v>
+        <v>0.002148517407476902</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.006328165531158447</v>
+        <v>0.03310023620724678</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.3757336735725403</v>
+        <v>0.002165782731026411</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.1440015733242035</v>
+        <v>0.0123710036277771</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.006101921666413546</v>
+        <v>0.01282909885048866</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.120269201695919</v>
+        <v>0.000706763006746769</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.2707152366638184</v>
+        <v>0.01011247932910919</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.1418120115995407</v>
+        <v>0.006914219819009304</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.02193598076701164</v>
+        <v>6.390977068804204e-05</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.2999657988548279</v>
+        <v>0.02059513330459595</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.2005362510681152</v>
+        <v>0.002297662198543549</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.07834604382514954</v>
+        <v>0.0003622234798967838</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.1446557641029358</v>
+        <v>0.001171238953247666</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.1519208252429962</v>
+        <v>0.003142546396702528</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.03369829803705215</v>
+        <v>0.01534366793930531</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.3104302287101746</v>
+        <v>0.04205760732293129</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.06428740173578262</v>
+        <v>0.003369043814018369</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.1029354631900787</v>
+        <v>0.003783989232033491</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.06183318793773651</v>
+        <v>0.01248364895582199</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0183496605604887</v>
+        <v>0.01280461251735687</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.02404500544071198</v>
+        <v>0.007461797446012497</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.1266270875930786</v>
+        <v>1.881876960396767e-05</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.04390780255198479</v>
+        <v>0.01489073410630226</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.08030415326356888</v>
+        <v>0.018256526440382</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1195132657885551</v>
+        <v>0.02958262525498867</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.03976990282535553</v>
+        <v>0.001220209058374166</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.09820593893527985</v>
+        <v>0.001709299976937473</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.03328153491020203</v>
+        <v>0.003616711124777794</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.08718419820070267</v>
+        <v>0.01034630369395018</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.07053370773792267</v>
+        <v>6.667128764092922e-05</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.04296132177114487</v>
+        <v>0.002439079806208611</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.04797929525375366</v>
+        <v>0.004093569703400135</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.222085103392601</v>
+        <v>0.02205624058842659</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0945337787270546</v>
+        <v>0.04723165929317474</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.02990000694990158</v>
+        <v>0.005117712542414665</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.05131715908646584</v>
+        <v>0.002246622694656253</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.1014048159122467</v>
+        <v>0.01295206137001514</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.06326445192098618</v>
+        <v>0.01971680298447609</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.05196261778473854</v>
+        <v>0.0006163890357129276</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.04195091128349304</v>
+        <v>0.009285468608140945</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.1412139683961868</v>
+        <v>0.007560232188552618</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.06025717407464981</v>
+        <v>0.01600774377584457</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.1479386240243912</v>
+        <v>0.02928575128316879</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.05910946801304817</v>
+        <v>0.0005285213701426983</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.06426917016506195</v>
+        <v>0.0004519050708040595</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.04282328858971596</v>
+        <v>2.064910950139165e-05</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0872637927532196</v>
+        <v>0.007308744825422764</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.06452436745166779</v>
+        <v>0.001100104884244502</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.1181994080543518</v>
+        <v>0.0001688498887233436</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.05633803084492683</v>
+        <v>0.005168910603970289</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.1843642741441727</v>
+        <v>0.004219771362841129</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.09762720018625259</v>
+        <v>0.04377174749970436</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.1148952171206474</v>
+        <v>0.0022986875846982</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.3652323186397552</v>
+        <v>0.001393980579450727</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.3252556324005127</v>
+        <v>0.01596836559474468</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.1913900077342987</v>
+        <v>0.001239490928128362</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.009174719452857971</v>
+        <v>0.003549169283360243</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.06296899914741516</v>
+        <v>0.01754258573055267</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.5047820210456848</v>
+        <v>0.01447666715830564</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.06351166218519211</v>
+        <v>0.01483992952853441</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.06296582520008087</v>
+        <v>0.01692327298223972</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.08480576425790787</v>
+        <v>0.001738856080919504</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.1941324174404144</v>
+        <v>0.008426643908023834</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.06963670253753662</v>
+        <v>0.001777484780177474</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.3199929893016815</v>
+        <v>0.007047470659017563</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.2617573738098145</v>
+        <v>0.002963911974802613</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.1514696776866913</v>
+        <v>0.01293439604341984</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.1484633982181549</v>
+        <v>0.002701994031667709</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.008908037096261978</v>
+        <v>0.01765377260744572</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.02167093008756638</v>
+        <v>0.02410221286118031</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.009949319064617157</v>
+        <v>0.001472457777708769</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0858849436044693</v>
+        <v>0.00154444994404912</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.08908959478139877</v>
+        <v>0.008522892370820045</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.2841821312904358</v>
+        <v>0.02557907812297344</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.07695171236991882</v>
+        <v>0.01495398208498955</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.3089238405227661</v>
+        <v>0.01290265563875437</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.1021168157458305</v>
+        <v>0.01339105051010847</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.1573337018489838</v>
+        <v>0.00381097849458456</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.02913840673863888</v>
+        <v>0.017462108284235</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.01714110560715199</v>
+        <v>0.008226647973060608</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.1209401115775108</v>
+        <v>0.003889197716489434</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.1172255426645279</v>
+        <v>0.003903292352333665</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0793517604470253</v>
+        <v>0.01081844139844179</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.1236917674541473</v>
+        <v>0.002345472341403365</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.1403718292713165</v>
+        <v>0.001374267041683197</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.08630815148353577</v>
+        <v>0.002595974132418633</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.05694621801376343</v>
+        <v>0.005948910024017096</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.2666414380073547</v>
+        <v>0.01408277172595263</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.02226405218243599</v>
+        <v>0.00432680593803525</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.02555201947689056</v>
+        <v>0.009872954338788986</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.1701973378658295</v>
+        <v>0.002230586018413305</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.04741469025611877</v>
+        <v>0.01169564481824636</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.02177554741501808</v>
+        <v>0.003466180991381407</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.1068791002035141</v>
+        <v>0.001337370369583368</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.03361441195011139</v>
+        <v>0.02394942007958889</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.04509728774428368</v>
+        <v>0.02068590931594372</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.1666128784418106</v>
+        <v>0.03255980834364891</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.09066347777843475</v>
+        <v>0.001749651972204447</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.07881546020507812</v>
+        <v>0.003114709164947271</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.07652713358402252</v>
+        <v>0.002354004653170705</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.06972768902778625</v>
+        <v>0.006233743857592344</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.002854913473129272</v>
+        <v>0.001689946046099067</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.09212818741798401</v>
+        <v>0.001215574331581593</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.01824617199599743</v>
+        <v>0.006659904029220343</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.05765008553862572</v>
+        <v>0.002535301260650158</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.1104877218604088</v>
+        <v>0.01427373476326466</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.05433511734008789</v>
+        <v>0.01107903942465782</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.2568133473396301</v>
+        <v>0.000528123346157372</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.2322685569524765</v>
+        <v>0.01030788756906986</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.08874413371086121</v>
+        <v>0.00829484686255455</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.2223994433879852</v>
+        <v>0.007718875072896481</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.139289602637291</v>
+        <v>0.001722826156765223</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.04322400689125061</v>
+        <v>0.0195192489773035</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.07366014271974564</v>
+        <v>0.03883283585309982</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.3173390328884125</v>
+        <v>0.009414207190275192</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.08726052194833755</v>
+        <v>0.004659521859139204</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.2550525963306427</v>
+        <v>0.02037889137864113</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.2200842201709747</v>
+        <v>0.008566414006054401</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.09501743316650391</v>
+        <v>0.01025417167693377</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.1868745684623718</v>
+        <v>0.01445704605430365</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.06960752606391907</v>
+        <v>0.02860312722623348</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.01381959021091461</v>
+        <v>0.01712981797754765</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.128784105181694</v>
+        <v>0.02015071175992489</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.004971100017428398</v>
+        <v>0.01474550645798445</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0220407247543335</v>
+        <v>0.009087370708584785</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.2254305928945541</v>
+        <v>0.01211124286055565</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.2759123742580414</v>
+        <v>0.009941825643181801</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.1478007733821869</v>
+        <v>0.006337134633213282</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.2823810875415802</v>
+        <v>0.002003852277994156</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.3293647468090057</v>
+        <v>0.0002714656293392181</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.06166712939739227</v>
+        <v>0.01993590034544468</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.1113482117652893</v>
+        <v>0.04251891374588013</v>
       </c>
       <c r="B6" t="n">
-        <v>1.095231890678406</v>
+        <v>0.9870152473449707</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06800443679094315</v>
+        <v>0.06429874897003174</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6454578042030334</v>
+        <v>0.8649274110794067</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3061586320400238</v>
+        <v>0.3900923132896423</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1995925754308701</v>
+        <v>0.379645049571991</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1813975125551224</v>
+        <v>0.1088158413767815</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01460087299346924</v>
+        <v>0.2039331197738647</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06188017129898071</v>
+        <v>0.0579717718064785</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1351926028728485</v>
+        <v>0.1741984486579895</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8725295662879944</v>
+        <v>0.9304342865943909</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002879224251955748</v>
+        <v>0.2213455438613892</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6028589606285095</v>
+        <v>1.035873174667358</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3929459452629089</v>
+        <v>0.5832340121269226</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2310909330844879</v>
+        <v>0.3222374618053436</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1119096279144287</v>
+        <v>0.125825971364975</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1771247833967209</v>
+        <v>0.009934829548001289</v>
       </c>
       <c r="R6" t="n">
-        <v>0.08586852252483368</v>
+        <v>0.07899454981088638</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03394445404410362</v>
+        <v>0.02529412321746349</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1447838246822357</v>
+        <v>0.03658289462327957</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03776326775550842</v>
+        <v>0.003791522234678268</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0247910562902689</v>
+        <v>0.04591740667819977</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0243854895234108</v>
+        <v>0.1160069853067398</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1594122350215912</v>
+        <v>0.135695606470108</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1723713427782059</v>
+        <v>0.1646547466516495</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01542048528790474</v>
+        <v>0.09567978978157043</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1225583925843239</v>
+        <v>0.04609988257288933</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.08744996041059494</v>
+        <v>0.05232489109039307</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1506492644548416</v>
+        <v>0.1974273473024368</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.004016140475869179</v>
+        <v>0.002582973800599575</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.01014899741858244</v>
+        <v>0.2071088850498199</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.04339594766497612</v>
+        <v>0.07817536592483521</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.1106496453285217</v>
+        <v>0.01095432601869106</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.1596170514822006</v>
+        <v>0.09073023498058319</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0245371013879776</v>
+        <v>0.1169128715991974</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.03599731624126434</v>
+        <v>0.108508825302124</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.04752424359321594</v>
+        <v>0.0112594049423933</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.1449525356292725</v>
+        <v>0.2799639701843262</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.00288823526352644</v>
+        <v>0.03055878728628159</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.003672436811029911</v>
+        <v>0.141456127166748</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.0485750176012516</v>
+        <v>0.181935578584671</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.05142317712306976</v>
+        <v>0.1777940541505814</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.07710245251655579</v>
+        <v>0.02277026325464249</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.1249107867479324</v>
+        <v>0.004227680154144764</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.08516031503677368</v>
+        <v>0.08209692686796188</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.01724411174654961</v>
+        <v>0.06183870881795883</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.6810722947120667</v>
+        <v>0.5837022662162781</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.02070554718375206</v>
+        <v>0.006459403783082962</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.112443819642067</v>
+        <v>0.3846436738967896</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.04408381879329681</v>
+        <v>0.4789547026157379</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.027070676907897</v>
+        <v>0.1360913217067719</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.03110198676586151</v>
+        <v>0.00756998173892498</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.1660894453525543</v>
+        <v>0.2020260840654373</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.09731458127498627</v>
+        <v>0.1366609483957291</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.003798365592956543</v>
+        <v>0.06804010272026062</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.1507467329502106</v>
+        <v>0.2668803930282593</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.1445741504430771</v>
+        <v>0.1854922622442245</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.1194662004709244</v>
+        <v>0.05452772229909897</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.4079165756702423</v>
+        <v>0.2109414488077164</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.02673979103565216</v>
+        <v>0.1847197860479355</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.2247103750705719</v>
+        <v>0.03456459194421768</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.1695616841316223</v>
+        <v>0.1332001388072968</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.06488747149705887</v>
+        <v>0.1724786460399628</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.1039906144142151</v>
+        <v>0.05494758486747742</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.05462365970015526</v>
+        <v>0.0898306742310524</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.01869426108896732</v>
+        <v>0.03008848428726196</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0004974731709808111</v>
+        <v>0.0464065708220005</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.002090525347739458</v>
+        <v>0.1766868680715561</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.1030349433422089</v>
+        <v>0.07520265132188797</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.09168163686990738</v>
+        <v>0.01475522480905056</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.1097195595502853</v>
+        <v>0.07302556931972504</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.07825633883476257</v>
+        <v>0.02695648372173309</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.03011143766343594</v>
+        <v>0.0161108672618866</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.3871001303195953</v>
+        <v>0.352348655462265</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.07621794193983078</v>
+        <v>0.01213835179805756</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.06469081342220306</v>
+        <v>0.2229530960321426</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0138129498809576</v>
+        <v>0.1603789478540421</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.06067545339465141</v>
+        <v>0.1936055123806</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.05256615579128265</v>
+        <v>0.1497502475976944</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.02593953907489777</v>
+        <v>0.01112487819045782</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.0969274491071701</v>
+        <v>0.03743565827608109</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.02534619532525539</v>
+        <v>0.02090129815042019</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.1711404621601105</v>
+        <v>0.3071717619895935</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.04848719388246536</v>
+        <v>0.01115710567682981</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.09912188351154327</v>
+        <v>0.2183327972888947</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.04699857532978058</v>
+        <v>0.07717938721179962</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.06316830217838287</v>
+        <v>0.03353910520672798</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.08170430362224579</v>
+        <v>0.02020224183797836</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.01518448628485203</v>
+        <v>0.06140905618667603</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.02828076481819153</v>
+        <v>0.03787190467119217</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.1522742360830307</v>
+        <v>0.02780644409358501</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.008481196127831936</v>
+        <v>0.5407081246376038</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.001436267979443073</v>
+        <v>0.1478996425867081</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.1679067611694336</v>
+        <v>0.1332673132419586</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.1197488978505135</v>
+        <v>0.06043529883027077</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.1254556775093079</v>
+        <v>0.001462862826883793</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.1258431673049927</v>
+        <v>0.04338853433728218</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.1822478771209717</v>
+        <v>0.006358925718814135</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.01476594619452953</v>
+        <v>0.01508098654448986</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.02437560819089413</v>
+        <v>0.0007195211946964264</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.1785843372344971</v>
+        <v>0.3114993572235107</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.07121844589710236</v>
+        <v>0.002730673179030418</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.1293626576662064</v>
+        <v>0.2287338823080063</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.04930347576737404</v>
+        <v>0.08914052695035934</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.08807365596294403</v>
+        <v>0.0336507074534893</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.08128294348716736</v>
+        <v>0.001390775665640831</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.02150479331612587</v>
+        <v>0.0681266263127327</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.003180030733346939</v>
+        <v>0.03183742612600327</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.02706868946552277</v>
+        <v>0.2053571939468384</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.168300673365593</v>
+        <v>0.3019885420799255</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.01847075112164021</v>
+        <v>0.1124722212553024</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.3719161152839661</v>
+        <v>0.3330821096897125</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1867530643939972</v>
+        <v>0.1615656316280365</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.09015087783336639</v>
+        <v>0.02260315604507923</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.1035215109586716</v>
+        <v>0.08106102049350739</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.1473397016525269</v>
+        <v>0.3243538737297058</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.02611979469656944</v>
+        <v>0.03316552564501762</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.03727630153298378</v>
+        <v>0.1391663253307343</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.09651459008455276</v>
+        <v>0.1450375765562057</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.04657551273703575</v>
+        <v>0.009763886220753193</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.07393741607666016</v>
+        <v>0.3020181655883789</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.124818466603756</v>
+        <v>0.1487208604812622</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.007110543549060822</v>
+        <v>0.1651997715234756</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.05633092299103737</v>
+        <v>0.1932408064603806</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.01705209910869598</v>
+        <v>0.05065229907631874</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.03562036156654358</v>
+        <v>0.2260199040174484</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.04852740839123726</v>
+        <v>0.02562844567000866</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.002673404291272163</v>
+        <v>0.246583878993988</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.1267382055521011</v>
+        <v>0.0142422690987587</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.02469880320131779</v>
+        <v>0.1746414005756378</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.1179514527320862</v>
+        <v>0.1158681437373161</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.02749589458107948</v>
+        <v>0.1178720891475677</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.02499443478882313</v>
+        <v>0.05622410774230957</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.06248727068305016</v>
+        <v>0.3999007940292358</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.003531109541654587</v>
+        <v>0.2361211329698563</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.009426664561033249</v>
+        <v>0.09750892221927643</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.1469501107931137</v>
+        <v>0.2533209025859833</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.04371432214975357</v>
+        <v>0.0582311823964119</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.08284732699394226</v>
+        <v>0.1024081483483315</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.1598118543624878</v>
+        <v>0.1511741876602173</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.01085148006677628</v>
+        <v>0.02541408687829971</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.1154056042432785</v>
+        <v>0.03604544699192047</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.05150067061185837</v>
+        <v>0.0858323723077774</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.03079402446746826</v>
+        <v>0.02418453618884087</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.01913832686841488</v>
+        <v>0.0404953621327877</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.1473867446184158</v>
+        <v>0.1973695158958435</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.1187180206179619</v>
+        <v>0.08818933367729187</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.1036766618490219</v>
+        <v>0.09934400767087936</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.1403514295816422</v>
+        <v>0.06319873780012131</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.204549103975296</v>
+        <v>0.1253200620412827</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.08233866095542908</v>
+        <v>0.1298000663518906</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.01776434853672981</v>
+        <v>0.06884203106164932</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.002730106934905052</v>
+        <v>0.09895098209381104</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.004445435479283333</v>
+        <v>0.03040589578449726</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.186440497636795</v>
+        <v>0.3416382074356079</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.04049859195947647</v>
+        <v>0.03461014851927757</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.1233251318335533</v>
+        <v>0.2440100014209747</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.04454239830374718</v>
+        <v>0.06277472525835037</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.08923529833555222</v>
+        <v>0.02422219701111317</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.09239993244409561</v>
+        <v>0.006638962309807539</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.01784356497228146</v>
+        <v>0.09776105731725693</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.03017788380384445</v>
+        <v>0.04249363392591476</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.0137175191193819</v>
+        <v>0.02220767363905907</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.09380528330802917</v>
+        <v>0.007594656199216843</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.04277577623724937</v>
+        <v>0.09072484821081161</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.1076422482728958</v>
+        <v>0.07901155948638916</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.06978078931570053</v>
+        <v>0.09203559160232544</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.03912573680281639</v>
+        <v>0.1621735990047455</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.0423041395843029</v>
+        <v>0.08581719547510147</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.02246911823749542</v>
+        <v>0.2787851095199585</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.07277674973011017</v>
+        <v>0.05041593685746193</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.0595298558473587</v>
+        <v>0.2650021910667419</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.08384273201227188</v>
+        <v>0.2295093238353729</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.08870717138051987</v>
+        <v>0.07224747538566589</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.01006658375263214</v>
+        <v>0.2868868112564087</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.03257647901773453</v>
+        <v>0.2028627693653107</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.02851275727152824</v>
+        <v>0.2101345658302307</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.0836508721113205</v>
+        <v>0.09692703187465668</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.1313945651054382</v>
+        <v>0.09117360413074493</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.1020302698016167</v>
+        <v>0.2944039404392242</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.09625598043203354</v>
+        <v>0.105401411652565</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.02664508298039436</v>
+        <v>0.2303375005722046</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.03526414930820465</v>
+        <v>0.1236993372440338</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.03641732782125473</v>
+        <v>0.1038539409637451</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.07962102442979813</v>
+        <v>0.3966216146945953</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.06925023347139359</v>
+        <v>0.04153468832373619</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.3570533990859985</v>
+        <v>0.2821316719055176</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.007797360420227051</v>
+        <v>0.0259835422039032</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.02661538869142532</v>
+        <v>0.0930534228682518</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.002797009889036417</v>
+        <v>0.1315757781267166</v>
       </c>
       <c r="B7" t="n">
-        <v>0.09571485221385956</v>
+        <v>0.7722026109695435</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001752968761138618</v>
+        <v>0.04050996154546738</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02503354288637638</v>
+        <v>0.1252095550298691</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01999366655945778</v>
+        <v>0.05121632665395737</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06185952946543694</v>
+        <v>1.139826059341431</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007390493061393499</v>
+        <v>0.1825345456600189</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01295948028564453</v>
+        <v>0.4047221541404724</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002418476855382323</v>
+        <v>0.03649147599935532</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01031496189534664</v>
+        <v>0.0133146196603775</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07659544795751572</v>
+        <v>0.9025721549987793</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002489184262230992</v>
+        <v>0.1066709756851196</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03909167647361755</v>
+        <v>0.08995607495307922</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01488268841058016</v>
+        <v>0.449977695941925</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06191537529230118</v>
+        <v>1.044022917747498</v>
       </c>
       <c r="P7" t="n">
-        <v>0.008324014022946358</v>
+        <v>0.0218854583799839</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.005951801314949989</v>
+        <v>0.3069531321525574</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01401769928634167</v>
+        <v>0.08220786601305008</v>
       </c>
       <c r="S7" t="n">
-        <v>0.004702678881585598</v>
+        <v>0.1684922724962234</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01637611351907253</v>
+        <v>0.1578773409128189</v>
       </c>
       <c r="U7" t="n">
-        <v>0.004207960795611143</v>
+        <v>0.3242032527923584</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008473510853946209</v>
+        <v>0.02058276906609535</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0008178348653018475</v>
+        <v>0.1671507805585861</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01382341329008341</v>
+        <v>0.2243610322475433</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.006076560821384192</v>
+        <v>0.2673627138137817</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002202778123319149</v>
+        <v>0.1898535192012787</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.003512123599648476</v>
+        <v>0.03535261377692223</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.005177415907382965</v>
+        <v>0.2011497616767883</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.009863180108368397</v>
+        <v>0.2624052166938782</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.001164495362900198</v>
+        <v>0.1037764847278595</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0003643921809270978</v>
+        <v>0.386970579624176</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.003175567835569382</v>
+        <v>0.04153532162308693</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.006434996612370014</v>
+        <v>0.1890026777982712</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.005653864704072475</v>
+        <v>0.1118663549423218</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.004818566143512726</v>
+        <v>0.3787665665149689</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.007554545532912016</v>
+        <v>0.2004616409540176</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.004606243222951889</v>
+        <v>0.07158044725656509</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.006979911122471094</v>
+        <v>0.08800208568572998</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.003745442721992731</v>
+        <v>0.02238842844963074</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.004054671619087458</v>
+        <v>0.04871103912591934</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.005527289118617773</v>
+        <v>0.09481737017631531</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.01133279781788588</v>
+        <v>0.1787824630737305</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.116395186632872e-05</v>
+        <v>0.2379923760890961</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.003574694972485304</v>
+        <v>0.2116501480340958</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.01044792681932449</v>
+        <v>0.1168908849358559</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.008810568600893021</v>
+        <v>0.1476605981588364</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.06395534425973892</v>
+        <v>0.7167778015136719</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.002784874755889177</v>
+        <v>0.2128381580114365</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.006329371128231287</v>
+        <v>0.08085974305868149</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0128356758505106</v>
+        <v>0.4420320689678192</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.03491751849651337</v>
+        <v>0.5756367444992065</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.001871904823929071</v>
+        <v>0.1950656920671463</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.008049137890338898</v>
+        <v>0.002289164811372757</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.007518841419368982</v>
+        <v>0.058983214199543</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.003371120430529118</v>
+        <v>0.05785834789276123</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02155201509594917</v>
+        <v>0.1669516712427139</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.01068427320569754</v>
+        <v>0.1749636232852936</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.008213956840336323</v>
+        <v>0.3141922652721405</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.01780402474105358</v>
+        <v>0.1551080942153931</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.021733608096838</v>
+        <v>0.2669966518878937</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.005425821524113417</v>
+        <v>0.1845145374536514</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.002988135907799006</v>
+        <v>0.2833985686302185</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.004068126901984215</v>
+        <v>0.2194972932338715</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.003384669311344624</v>
+        <v>0.118105560541153</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.003073330037295818</v>
+        <v>0.1790999472141266</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.003030032385140657</v>
+        <v>0.04209423065185547</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.009384585544466972</v>
+        <v>0.1098809391260147</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.005786221474409103</v>
+        <v>0.07124541699886322</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0001623267307877541</v>
+        <v>0.1700491011142731</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.000376479234546423</v>
+        <v>0.2718843221664429</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.008913308382034302</v>
+        <v>0.05072628706693649</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0002252093981951475</v>
+        <v>0.1124674454331398</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.009768526069819927</v>
+        <v>0.07236853241920471</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.03436671569943428</v>
+        <v>0.244452953338623</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.003203649073839188</v>
+        <v>0.2687088251113892</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.0008358745835721493</v>
+        <v>0.04979144781827927</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.004015917424112558</v>
+        <v>0.2620740830898285</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0143305417150259</v>
+        <v>0.5268862843513489</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.005911519285291433</v>
+        <v>0.3872077465057373</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.003942728973925114</v>
+        <v>0.1317493617534637</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.00030354387126863</v>
+        <v>0.08003158122301102</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.004145339131355286</v>
+        <v>0.01078058127313852</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.01599486544728279</v>
+        <v>0.2677655816078186</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.004309189040213823</v>
+        <v>0.02592077478766441</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.005988424643874168</v>
+        <v>0.002995815826579928</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.003297906136140227</v>
+        <v>0.03270005434751511</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.009471531957387924</v>
+        <v>0.2668721675872803</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.002668218454346061</v>
+        <v>0.07840206474065781</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0009746425785124302</v>
+        <v>0.0730958878993988</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0003135311126243323</v>
+        <v>0.003868956118822098</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.01346215233206749</v>
+        <v>0.1677427291870117</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.01203803811222315</v>
+        <v>0.4698951840400696</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.456734025850892e-06</v>
+        <v>0.4148134589195251</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.009821323677897453</v>
+        <v>0.3243036568164825</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0004045513924211264</v>
+        <v>0.110430546104908</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.002684739883989096</v>
+        <v>0.2384114861488342</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.006910447031259537</v>
+        <v>0.02601331658661366</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.006678131874650717</v>
+        <v>0.1779799908399582</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.009607506915926933</v>
+        <v>0.1324589550495148</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.002401556819677353</v>
+        <v>0.02290347963571548</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.01346877217292786</v>
+        <v>0.2444465756416321</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.006086469162255526</v>
+        <v>0.02063092216849327</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.00823697168380022</v>
+        <v>0.008410700596868992</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.001589609310030937</v>
+        <v>0.008368782699108124</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.01290266867727041</v>
+        <v>0.2474237680435181</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.001221237238496542</v>
+        <v>0.08611533790826797</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.003959469497203827</v>
+        <v>0.01944717578589916</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.002276130951941013</v>
+        <v>0.02795987948775291</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.004585922230035067</v>
+        <v>0.3217983543872833</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.007324631325900555</v>
+        <v>0.1513833701610565</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.003518593963235617</v>
+        <v>0.2505889534950256</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.01248852349817753</v>
+        <v>0.09454769641160965</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01600227132439613</v>
+        <v>0.08575119078159332</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.02527616918087006</v>
+        <v>0.3900810480117798</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.006029008887708187</v>
+        <v>0.1347264498472214</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0146886333823204</v>
+        <v>0.20967797935009</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.01146197412163019</v>
+        <v>0.2840030789375305</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0002258616732433438</v>
+        <v>0.005136311054229736</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.006123104132711887</v>
+        <v>0.1123919785022736</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.007897131145000458</v>
+        <v>0.06371652334928513</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0114752259105444</v>
+        <v>0.1357568800449371</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.003078042762354016</v>
+        <v>0.004483029246330261</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.002520757261663675</v>
+        <v>0.1143743395805359</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.003977485466748476</v>
+        <v>0.04856295883655548</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.001059410395100713</v>
+        <v>0.05518218874931335</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.007911808788776398</v>
+        <v>0.002863168716430664</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.004912112839519978</v>
+        <v>0.06917686760425568</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.006509478203952312</v>
+        <v>0.1751745194196701</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.008202655240893364</v>
+        <v>0.0499589815735817</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.003958383575081825</v>
+        <v>0.06015073508024216</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.001577933318912983</v>
+        <v>0.0294465646147728</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.003087029792368412</v>
+        <v>0.1947790682315826</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.002989830449223518</v>
+        <v>0.02300662361085415</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.009012095630168915</v>
+        <v>0.1223186403512955</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.004680910613387823</v>
+        <v>0.2595449686050415</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.002755505964159966</v>
+        <v>0.1165536195039749</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.01047730073332787</v>
+        <v>0.1115812733769417</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.001211861148476601</v>
+        <v>0.1459900438785553</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.005157495848834515</v>
+        <v>0.01802293956279755</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.006291210185736418</v>
+        <v>0.0238393135368824</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.01433024927973747</v>
+        <v>0.3099856674671173</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.001958056353032589</v>
+        <v>0.001799669465981424</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.006952023599296808</v>
+        <v>0.01660796999931335</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.003741525812074542</v>
+        <v>0.004451577086001635</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.000306592759443447</v>
+        <v>0.009195530787110329</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.007969005033373833</v>
+        <v>0.1506314128637314</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.004972456023097038</v>
+        <v>0.1913613379001617</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.01027871109545231</v>
+        <v>0.1027754172682762</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.01103127934038639</v>
+        <v>0.165085107088089</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.01619677618145943</v>
+        <v>0.2314279079437256</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.00722257187590003</v>
+        <v>0.0266750194132328</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.006169636733829975</v>
+        <v>0.05057298019528389</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.006764632649719715</v>
+        <v>0.03722359612584114</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.002999272430315614</v>
+        <v>0.00728425569832325</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.01366503164172173</v>
+        <v>0.2573692202568054</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.002313306322321296</v>
+        <v>0.02389947697520256</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.004591917153447866</v>
+        <v>0.01293438393622637</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.001254887785762548</v>
+        <v>0.07745477557182312</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.01059034466743469</v>
+        <v>0.2630271017551422</v>
       </c>
       <c r="FD7" t="n">
-        <v>3.534711140673608e-05</v>
+        <v>0.08393258601427078</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0003553929273039103</v>
+        <v>0.07664766162633896</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.001245854306034744</v>
+        <v>0.02178049273788929</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.001556385424919426</v>
+        <v>0.1332104951143265</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.006606640759855509</v>
+        <v>0.09614291787147522</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.007604362443089485</v>
+        <v>0.1360440254211426</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.01379187311977148</v>
+        <v>0.08784747123718262</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.006499324925243855</v>
+        <v>0.0302739106118679</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.007398007437586784</v>
+        <v>0.3042762875556946</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.001172746066004038</v>
+        <v>0.200356587767601</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.001591410953551531</v>
+        <v>0.195365846157074</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.006765551865100861</v>
+        <v>0.2451802790164948</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.003344160271808505</v>
+        <v>0.2792268991470337</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.04135663062334061</v>
+        <v>0.1496385484933853</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.001343946787528694</v>
+        <v>0.09382237493991852</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.01769636571407318</v>
+        <v>0.2680647671222687</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.0004674186930060387</v>
+        <v>0.1817565411329269</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.007040631026029587</v>
+        <v>0.1795272827148438</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.001606010948307812</v>
+        <v>0.005743445828557014</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.0120046166703105</v>
+        <v>0.2274714112281799</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.005551587790250778</v>
+        <v>0.01662147231400013</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.007233138661831617</v>
+        <v>0.221948653459549</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.007243790198117495</v>
+        <v>0.0165877565741539</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.001286532147787511</v>
+        <v>0.09345895051956177</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.008994601666927338</v>
+        <v>0.04509087279438972</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.03780226409435272</v>
+        <v>0.4077448546886444</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.01418584957718849</v>
+        <v>0.2788335978984833</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.0187055915594101</v>
+        <v>0.0566086582839489</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.006221191957592964</v>
+        <v>0.01583719067275524</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.004648556932806969</v>
+        <v>0.2788786590099335</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.003330378793179989</v>
+        <v>0.06244466453790665</v>
       </c>
       <c r="B8" t="n">
-        <v>0.09375151246786118</v>
+        <v>0.1722142994403839</v>
       </c>
       <c r="C8" t="n">
-        <v>0.005211139563471079</v>
+        <v>0.01051084883511066</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06487380713224411</v>
+        <v>0.2101704776287079</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03415476530790329</v>
+        <v>0.0613502711057663</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01689414493739605</v>
+        <v>0.09887407720088959</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005062862299382687</v>
+        <v>0.03073561191558838</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004150971304625273</v>
+        <v>0.04646868258714676</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003567105857655406</v>
+        <v>0.001862225471995771</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000856109312735498</v>
+        <v>0.1020773351192474</v>
       </c>
       <c r="K8" t="n">
-        <v>0.07584302872419357</v>
+        <v>0.1328903138637543</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001063371310010552</v>
+        <v>0.06656279414892197</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03812723234295845</v>
+        <v>0.2952107787132263</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02898566052317619</v>
+        <v>0.09208215773105621</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01695765741169453</v>
+        <v>0.09759724885225296</v>
       </c>
       <c r="P8" t="n">
-        <v>0.005709740333259106</v>
+        <v>0.07454542815685272</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009243421256542206</v>
+        <v>0.0007330542430281639</v>
       </c>
       <c r="R8" t="n">
-        <v>0.009684005752205849</v>
+        <v>0.01581749878823757</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002249743090942502</v>
+        <v>0.02611812576651573</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01404185872524977</v>
+        <v>0.01330482680350542</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002199995331466198</v>
+        <v>0.00478457473218441</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0007279070559889078</v>
+        <v>0.006170173175632954</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0007513042073696852</v>
+        <v>0.06625578552484512</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01659606955945492</v>
+        <v>0.047939483076334</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01716757193207741</v>
+        <v>0.008067560382187366</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.005736536346375942</v>
+        <v>0.01374009810388088</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.004411484580487013</v>
+        <v>0.02360758185386658</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01102415286004543</v>
+        <v>0.03416375815868378</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01079595740884542</v>
+        <v>0.05601494014263153</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.583838067948818e-05</v>
+        <v>0.01826340518891811</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.00341159338131547</v>
+        <v>0.01572247035801411</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01663211546838284</v>
+        <v>0.02469477988779545</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.003436818718910217</v>
+        <v>0.01504525728523731</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0008086021989583969</v>
+        <v>0.00632802490144968</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.001553260954096913</v>
+        <v>0.001741250976920128</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.004294097889214754</v>
+        <v>0.03450233116745949</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.002275583334267139</v>
+        <v>0.03053819946944714</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01371095608919859</v>
+        <v>0.0488748736679554</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.002719904063269496</v>
+        <v>0.0317254476249218</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.002713133580982685</v>
+        <v>0.02832797542214394</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.005000887904316187</v>
+        <v>0.01735350117087364</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.008627868257462978</v>
+        <v>0.04317150264978409</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0003174373414367437</v>
+        <v>0.02815891616046429</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.00118412496522069</v>
+        <v>0.01623481512069702</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.00978283304721117</v>
+        <v>0.01448813080787659</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0136527344584465</v>
+        <v>0.02196480892598629</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.05917693674564362</v>
+        <v>0.1038882434368134</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.001158090075477958</v>
+        <v>0.01934417709708214</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.03117125667631626</v>
+        <v>0.1511531174182892</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.007656781934201717</v>
+        <v>0.1205124482512474</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.00408907700330019</v>
+        <v>0.01879698783159256</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.01708135381340981</v>
+        <v>0.005144020076841116</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.01166451536118984</v>
+        <v>0.02743028290569782</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.01009021699428558</v>
+        <v>0.02757486514747143</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.001397700048983097</v>
+        <v>0.01553019881248474</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.01644325442612171</v>
+        <v>0.0146179310977459</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.007300912402570248</v>
+        <v>0.0308322012424469</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.005045157857239246</v>
+        <v>0.06430670619010925</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.02558189071714878</v>
+        <v>0.06982559710741043</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.002259765984490514</v>
+        <v>0.0440111830830574</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.007842293940484524</v>
+        <v>0.02355102635920048</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.005349279381334782</v>
+        <v>0.0508459135890007</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.007597428280860186</v>
+        <v>0.04122455418109894</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.009743834845721722</v>
+        <v>0.02027342282235622</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.004072557669132948</v>
+        <v>0.01759769022464752</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.002607465256005526</v>
+        <v>0.03400004655122757</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0003270457964390516</v>
+        <v>0.002188639715313911</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.005000816658139229</v>
+        <v>0.03749523311853409</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.005678550340235233</v>
+        <v>0.01392155233770609</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.001199579797685146</v>
+        <v>0.004558121785521507</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.004195915535092354</v>
+        <v>0.00458906777203083</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.002109430031850934</v>
+        <v>0.0008521729614585638</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.009228836745023727</v>
+        <v>0.01943734660744667</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.03166471421718597</v>
+        <v>0.05920182168483734</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.008067550137639046</v>
+        <v>0.0085400165989995</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.01247831992805004</v>
+        <v>0.1106138527393341</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.006042639259248972</v>
+        <v>0.06840216368436813</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.007357730995863676</v>
+        <v>0.05735693499445915</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0008650778327137232</v>
+        <v>0.02076408267021179</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.01010077819228172</v>
+        <v>0.002911779563874006</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.008152102120220661</v>
+        <v>0.01409373339265585</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.001855816692113876</v>
+        <v>0.01120569836348295</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.01319824904203415</v>
+        <v>0.04631892219185829</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.002299024490639567</v>
+        <v>0.005832967814058065</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.008220759220421314</v>
+        <v>0.06685523688793182</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.002457953756675124</v>
+        <v>0.005964801181107759</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.003253310918807983</v>
+        <v>0.002725580474361777</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.005156891886144876</v>
+        <v>0.0046956492587924</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0001928682904690504</v>
+        <v>0.0122954323887825</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.001181801082566381</v>
+        <v>0.005590147338807583</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.01340728811919689</v>
+        <v>0.03130937367677689</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0005740635097026825</v>
+        <v>0.04917313158512115</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.001780074671842158</v>
+        <v>0.0380401574075222</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0118150981143117</v>
+        <v>0.0607462152838707</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.01669987849891186</v>
+        <v>0.0185166709125042</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.004554281011223793</v>
+        <v>0.01381387654691935</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.01147179398685694</v>
+        <v>0.0001365188509225845</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.02733912877738476</v>
+        <v>0.05046030879020691</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.005317148752510548</v>
+        <v>0.0220238920301199</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0009608865948393941</v>
+        <v>0.01223680563271046</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.01390662230551243</v>
+        <v>0.04701250791549683</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.003640991868451238</v>
+        <v>0.01167580205947161</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.01226869970560074</v>
+        <v>0.07208073884248734</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.003738552099093795</v>
+        <v>0.009961653500795364</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.008800311014056206</v>
+        <v>0.00689682736992836</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.004351003095507622</v>
+        <v>0.01786073110997677</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0002381107769906521</v>
+        <v>0.0130428671836853</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.001069810008630157</v>
+        <v>0.00606227945536375</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.00497167743742466</v>
+        <v>0.05024278163909912</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.02323515713214874</v>
+        <v>0.06981415301561356</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.001521081547252834</v>
+        <v>0.09115020930767059</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.03461992740631104</v>
+        <v>0.06383804231882095</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.00717084389179945</v>
+        <v>0.01394007261842489</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.004243490286171436</v>
+        <v>0.02671581506729126</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.007978511974215508</v>
+        <v>0.01739231124520302</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.008927218616008759</v>
+        <v>0.09008779376745224</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.002442787168547511</v>
+        <v>0.01876254193484783</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.006055024452507496</v>
+        <v>0.04357948899269104</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.01026446092873812</v>
+        <v>0.02966320142149925</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.005558821372687817</v>
+        <v>0.01219340041279793</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.008343187160789967</v>
+        <v>0.05763994157314301</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.001294670626521111</v>
+        <v>0.02790052071213722</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0005306957755237818</v>
+        <v>0.05052071437239647</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0005702623166143894</v>
+        <v>0.02386562898755074</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.001063809730112553</v>
+        <v>0.006877188570797443</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.003418499371036887</v>
+        <v>0.05626961588859558</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0006571093108505011</v>
+        <v>0.02222792990505695</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.003035537898540497</v>
+        <v>0.01343245059251785</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.006852020509541035</v>
+        <v>0.01385443471372128</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.000241113593801856</v>
+        <v>0.0521603487432003</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0002328082919120789</v>
+        <v>0.02155561558902264</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.005929774604737759</v>
+        <v>0.009420475922524929</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.005888558924198151</v>
+        <v>0.01764809153974056</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.002068291185423732</v>
+        <v>0.09845118969678879</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.001851813169196248</v>
+        <v>0.05599045380949974</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.003312557702884078</v>
+        <v>0.04972989112138748</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.00964523758739233</v>
+        <v>0.03011317178606987</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.003288405016064644</v>
+        <v>0.002505856566131115</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.02359175309538841</v>
+        <v>0.04180143401026726</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.008512596599757671</v>
+        <v>0.005030096974223852</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.005667468998581171</v>
+        <v>0.008492590859532356</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.004812305327504873</v>
+        <v>0.002150500193238258</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.005396399646997452</v>
+        <v>0.004585051909089088</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.001601724070496857</v>
+        <v>0.007811954710632563</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.005091396626085043</v>
+        <v>0.003889460116624832</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.009586361236870289</v>
+        <v>0.04554922506213188</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.006324457470327616</v>
+        <v>0.0003322204574942589</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.006620788015425205</v>
+        <v>0.02313740365207195</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.005461462307721376</v>
+        <v>0.02191433310508728</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.01960108801722527</v>
+        <v>0.04458002001047134</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.007437812630087137</v>
+        <v>0.03338891640305519</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.007108089979737997</v>
+        <v>0.02271928451955318</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.005440205801278353</v>
+        <v>0.05251039192080498</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.00119273504242301</v>
+        <v>0.006301548331975937</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.01359994616359472</v>
+        <v>0.04811611026525497</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.001007562852464616</v>
+        <v>0.001133492100052536</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.01037297025322914</v>
+        <v>0.07554390281438828</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.003246296430006623</v>
+        <v>0.006382809951901436</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.008085116744041443</v>
+        <v>3.003375604748726e-05</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.005104064475744963</v>
+        <v>0.01137587428092957</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.0001765319611877203</v>
+        <v>0.02347332425415516</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.001567102619446814</v>
+        <v>0.01093727722764015</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.001026556012220681</v>
+        <v>0.01060051005333662</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.003646205412223935</v>
+        <v>0.001919847447425127</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.001410581171512604</v>
+        <v>0.02244284003973007</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.01151811052113771</v>
+        <v>0.02256849594414234</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.001661239424720407</v>
+        <v>0.01497013214975595</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.001914142398163676</v>
+        <v>0.01951899565756321</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.005987586453557014</v>
+        <v>0.03784630447626114</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.00738395843654871</v>
+        <v>0.04593794047832489</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.01021627336740494</v>
+        <v>0.002708258107304573</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.006277363281697035</v>
+        <v>0.03267132863402367</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.0002278895117342472</v>
+        <v>0.08880801498889923</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.006126913242042065</v>
+        <v>0.03238943964242935</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.005554371979087591</v>
+        <v>0.1340920627117157</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.004491095431149006</v>
+        <v>0.08421966433525085</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.006023717112839222</v>
+        <v>0.05256897583603859</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.009254846721887589</v>
+        <v>0.01290139742195606</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.01060512568801641</v>
+        <v>0.02182044088840485</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.006319336127489805</v>
+        <v>0.07337343692779541</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.01078684348613024</v>
+        <v>0.01679396815598011</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.004821918439120054</v>
+        <v>0.0193474218249321</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.001229960005730391</v>
+        <v>0.02593037113547325</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.002680140547454357</v>
+        <v>0.03963136300444603</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.01596415415406227</v>
+        <v>0.08348625898361206</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.01078107394278049</v>
+        <v>0.004820560105144978</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.0203354749828577</v>
+        <v>0.06550620496273041</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.00251524243503809</v>
+        <v>0.0009653381421230733</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.001787164714187384</v>
+        <v>0.006728828884661198</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.321229875087738</v>
+        <v>0.1478789895772934</v>
       </c>
       <c r="B9" t="n">
-        <v>0.09441050887107849</v>
+        <v>0.0005640313029289246</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3606354892253876</v>
+        <v>0.09880448132753372</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05954400449991226</v>
+        <v>0.1144221052527428</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9609566926956177</v>
+        <v>0.03106822445988655</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1225154101848602</v>
+        <v>0.06627441942691803</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01682260632514954</v>
+        <v>0.01425654534250498</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01230856031179428</v>
+        <v>0.08207709342241287</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1487205922603607</v>
+        <v>0.04088026285171509</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2334082126617432</v>
+        <v>0.1979668140411377</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1349155008792877</v>
+        <v>0.03419854119420052</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08619767427444458</v>
+        <v>0.05816802754998207</v>
       </c>
       <c r="M9" t="n">
-        <v>0.134793683886528</v>
+        <v>0.05220376327633858</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7486727833747864</v>
+        <v>0.09082787483930588</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0002699438482522964</v>
+        <v>0.0521899089217186</v>
       </c>
       <c r="P9" t="n">
-        <v>0.08482435345649719</v>
+        <v>0.055721215903759</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1389646530151367</v>
+        <v>0.0509890541434288</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1780370324850082</v>
+        <v>0.006596572697162628</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01993334107100964</v>
+        <v>0.01563652977347374</v>
       </c>
       <c r="T9" t="n">
-        <v>0.12847900390625</v>
+        <v>0.1253682225942612</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2054896056652069</v>
+        <v>0.01979599520564079</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03952820971608162</v>
+        <v>0.04115887731313705</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02350533939898014</v>
+        <v>0.01865313015878201</v>
       </c>
       <c r="X9" t="n">
-        <v>0.07152473926544189</v>
+        <v>0.03043810278177261</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.007765683345496655</v>
+        <v>0.006307763047516346</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.006235445849597454</v>
+        <v>0.006171766668558121</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.07289913296699524</v>
+        <v>0.006501142866909504</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03665638715028763</v>
+        <v>0.1280075311660767</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.03761881962418556</v>
+        <v>0.01770389452576637</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.1552556306123734</v>
+        <v>0.02009374275803566</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.1790376305580139</v>
+        <v>0.01468308921903372</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.04818057268857956</v>
+        <v>0.0470631867647171</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.07737866044044495</v>
+        <v>0.04711094498634338</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.08574283868074417</v>
+        <v>0.007618288975208998</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.01986705511808395</v>
+        <v>0.04024120420217514</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.1348166167736053</v>
+        <v>0.007197460159659386</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.03758499026298523</v>
+        <v>0.04400046169757843</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.2387753129005432</v>
+        <v>0.1100273579359055</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.05406230688095093</v>
+        <v>0.01570541225373745</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0473710224032402</v>
+        <v>0.05574629828333855</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.03227898478507996</v>
+        <v>0.07498697936534882</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.07885420322418213</v>
+        <v>0.004870545119047165</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.08086036145687103</v>
+        <v>0.02816996537148952</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.06465604156255722</v>
+        <v>0.03712253272533417</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.1299889385700226</v>
+        <v>0.009620945900678635</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.2302952855825424</v>
+        <v>0.1388290375471115</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.2987423241138458</v>
+        <v>0.06453670561313629</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.3715847730636597</v>
+        <v>0.05785409361124039</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.1654088050127029</v>
+        <v>0.06460200250148773</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.7735544443130493</v>
+        <v>0.07942280173301697</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.1013095155358315</v>
+        <v>0.03081054426729679</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.06707969307899475</v>
+        <v>0.01134559419006109</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.08136340975761414</v>
+        <v>0.06817759573459625</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.09833382070064545</v>
+        <v>0.02174954302608967</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.07377061992883682</v>
+        <v>0.06873651593923569</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.4150322377681732</v>
+        <v>0.07017336040735245</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.003862310200929642</v>
+        <v>0.002172407228499651</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.1708314418792725</v>
+        <v>0.01585912331938744</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.3197038173675537</v>
+        <v>0.1029348373413086</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.3727091252803802</v>
+        <v>0.008998574689030647</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.055404894053936</v>
+        <v>0.03932518884539604</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.2686153948307037</v>
+        <v>0.08680135756731033</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.08208750188350677</v>
+        <v>0.003927969373762608</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.2017269432544708</v>
+        <v>0.01857522130012512</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.2172750383615494</v>
+        <v>0.01424911059439182</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.2455943524837494</v>
+        <v>0.003646752797067165</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.3206652402877808</v>
+        <v>0.01169810444116592</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.01846256479620934</v>
+        <v>0.004252171143889427</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.3261240720748901</v>
+        <v>0.01099216379225254</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.2520573735237122</v>
+        <v>0.0008427727152593434</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.006542011629790068</v>
+        <v>0.002233371138572693</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.2687731087207794</v>
+        <v>0.01635593920946121</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.05992353707551956</v>
+        <v>0.07107345014810562</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.07022499293088913</v>
+        <v>0.07327084988355637</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.05362610518932343</v>
+        <v>0.03664993122220039</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.1697016656398773</v>
+        <v>0.0402083620429039</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.3683861792087555</v>
+        <v>0.06908059865236282</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.1607734262943268</v>
+        <v>0.004358252510428429</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.01383578777313232</v>
+        <v>0.004312565084546804</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.1376677751541138</v>
+        <v>0.01286397874355316</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.2196455448865891</v>
+        <v>0.01949745789170265</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.04011623561382294</v>
+        <v>0.03384281694889069</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.04703203588724136</v>
+        <v>0.006488817278295755</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.07277775555849075</v>
+        <v>0.01501359976828098</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.1331294327974319</v>
+        <v>0.005973635707050562</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.09661633521318436</v>
+        <v>0.04492355138063431</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.03882666304707527</v>
+        <v>0.0195738859474659</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.01906425505876541</v>
+        <v>0.01101292856037617</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.05623585730791092</v>
+        <v>0.001790080219507217</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.01365496031939983</v>
+        <v>0.01100748125463724</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0756252110004425</v>
+        <v>0.02106506749987602</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.07512173056602478</v>
+        <v>0.02610551193356514</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.1373697519302368</v>
+        <v>0.02223612368106842</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.09513698518276215</v>
+        <v>0.05031290650367737</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.2347006648778915</v>
+        <v>0.0125773586332798</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0668472945690155</v>
+        <v>0.03568908199667931</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.08722394704818726</v>
+        <v>0.04185869917273521</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.0710190013051033</v>
+        <v>0.007028179243206978</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.1851362884044647</v>
+        <v>0.02865567989647388</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.03016930446028709</v>
+        <v>0.04852423444390297</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.05034535750746727</v>
+        <v>0.02416675165295601</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.06333945691585541</v>
+        <v>0.0206474419683218</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.1001561507582664</v>
+        <v>0.0009891536319628358</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.1178904622793198</v>
+        <v>0.02715344913303852</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.01479905657470226</v>
+        <v>0.02086596749722958</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.01272306591272354</v>
+        <v>0.01038370933383703</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.01589357480406761</v>
+        <v>0.008768681436777115</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.04566420242190361</v>
+        <v>0.01578971557319164</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.1861368268728256</v>
+        <v>0.02436511218547821</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.2162395864725113</v>
+        <v>0.02348019368946552</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.3129130601882935</v>
+        <v>0.0443282276391983</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.3207572996616364</v>
+        <v>0.006878498010337353</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.1855368614196777</v>
+        <v>0.0793190598487854</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.05429373309016228</v>
+        <v>0.1079658791422844</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.08063022792339325</v>
+        <v>0.002187814330682158</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.06488482654094696</v>
+        <v>0.000885901041328907</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.1076782643795013</v>
+        <v>0.03535980731248856</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.07931041717529297</v>
+        <v>0.03616498410701752</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.09976233541965485</v>
+        <v>0.002107655862346292</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.003612253814935684</v>
+        <v>0.01886720024049282</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.07109514623880386</v>
+        <v>0.01517150364816189</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.04536912217736244</v>
+        <v>0.03288325667381287</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.2098611146211624</v>
+        <v>0.00840846449136734</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.08705480396747589</v>
+        <v>0.03012442216277122</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.006519438698887825</v>
+        <v>0.0008742716163396835</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.2633334398269653</v>
+        <v>0.006772438995540142</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.08036772906780243</v>
+        <v>0.06264331936836243</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.03263691440224648</v>
+        <v>0.04438359290361404</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.06198879331350327</v>
+        <v>0.03037210181355476</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.08167765289545059</v>
+        <v>0.004072867333889008</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.223377600312233</v>
+        <v>0.004889435134828091</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.1802107840776443</v>
+        <v>0.01107844058424234</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.02879675105214119</v>
+        <v>0.01910245418548584</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.08317319303750992</v>
+        <v>0.03195593506097794</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.07719006389379501</v>
+        <v>0.04498402401804924</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.01983869448304176</v>
+        <v>0.019918417558074</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0963733121752739</v>
+        <v>0.06519250571727753</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.1747745722532272</v>
+        <v>0.0307511929422617</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.1305917799472809</v>
+        <v>0.0205871369689703</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.02929059416055679</v>
+        <v>0.0469890758395195</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.07673265784978867</v>
+        <v>0.01089226640760899</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.02581380680203438</v>
+        <v>0.03244120627641678</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.07299118489027023</v>
+        <v>0.001074540428817272</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.1919969916343689</v>
+        <v>3.72026115655899e-05</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.08972226083278656</v>
+        <v>0.04345078393816948</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.1444678604602814</v>
+        <v>0.008544635958969593</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.03593061864376068</v>
+        <v>0.01599912345409393</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.02215670421719551</v>
+        <v>0.01891851238906384</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.3334569931030273</v>
+        <v>0.01338311657309532</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.008580984547734261</v>
+        <v>0.001315721310675144</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.1885790377855301</v>
+        <v>0.03816128522157669</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.1006171554327011</v>
+        <v>0.02149298787117004</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.2671268284320831</v>
+        <v>0.009034395217895508</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.01512522250413895</v>
+        <v>0.04469278454780579</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.022788992151618</v>
+        <v>0.008024204522371292</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.04668896645307541</v>
+        <v>0.0307900533080101</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.08320211619138718</v>
+        <v>0.001326952828094363</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.1078482493758202</v>
+        <v>0.04045575484633446</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.1113098561763763</v>
+        <v>0.01628389023244381</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.01497406698763371</v>
+        <v>0.01013115234673023</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.01752779446542263</v>
+        <v>0.0123265665024519</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.05748855322599411</v>
+        <v>0.02343153953552246</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.08408934623003006</v>
+        <v>0.1057844758033752</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.2351785004138947</v>
+        <v>0.01248485408723354</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.098885178565979</v>
+        <v>0.05349091067910194</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.04460552707314491</v>
+        <v>0.05943658575415611</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.05342437699437141</v>
+        <v>0.09487588703632355</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.02480171993374825</v>
+        <v>0.03656088933348656</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.1146954894065857</v>
+        <v>0.01187138166278601</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.07738928496837616</v>
+        <v>0.01522322557866573</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.02973425947129726</v>
+        <v>0.01298629865050316</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.2804080545902252</v>
+        <v>0.09072984755039215</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.1074640154838562</v>
+        <v>0.1514167189598083</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.1521814316511154</v>
+        <v>0.1160456016659737</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.1491862237453461</v>
+        <v>0.04472774639725685</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.3462403416633606</v>
+        <v>0.0008460469543933868</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.1421146392822266</v>
+        <v>0.06496899574995041</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.07195335626602173</v>
+        <v>0.004169526975601912</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.2041413635015488</v>
+        <v>0.03200178593397141</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.04322579130530357</v>
+        <v>0.02575848624110222</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.1050997897982597</v>
+        <v>0.03621373698115349</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.159015417098999</v>
+        <v>0.08329363167285919</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.07287886738777161</v>
+        <v>0.03711486235260963</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.2139245271682739</v>
+        <v>0.005119009874761105</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.05049071460962296</v>
+        <v>0.03315478563308716</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.244797557592392</v>
+        <v>0.1311406642198563</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.07152631878852844</v>
+        <v>0.01293340604752302</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.04593114927411079</v>
+        <v>0.0006380500271916389</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.03476303815841675</v>
+        <v>0.007786649279296398</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.001558362622745335</v>
+        <v>0.07211565971374512</v>
       </c>
       <c r="B10" t="n">
-        <v>0.01457444299012423</v>
+        <v>0.6606547236442566</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00119552353862673</v>
+        <v>0.09207223355770111</v>
       </c>
       <c r="D10" t="n">
-        <v>0.007996306754648685</v>
+        <v>0.004717093892395496</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003510730108246207</v>
+        <v>0.08503775298595428</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01255436707288027</v>
+        <v>1.212004899978638</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002438461408019066</v>
+        <v>0.1440335065126419</v>
       </c>
       <c r="H10" t="n">
-        <v>0.004340299405157566</v>
+        <v>0.3475029170513153</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001013305969536304</v>
+        <v>0.01305089052766562</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0005668966332450509</v>
+        <v>0.0006685769185423851</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01132075767964125</v>
+        <v>0.7608839273452759</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0006898075225763023</v>
+        <v>0.1396607756614685</v>
       </c>
       <c r="M10" t="n">
-        <v>0.00840312521904707</v>
+        <v>0.006176353432238102</v>
       </c>
       <c r="N10" t="n">
-        <v>0.003630925435572863</v>
+        <v>0.3269156813621521</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0121797202154994</v>
+        <v>1.101368546485901</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001546982675790787</v>
+        <v>0.04718220978975296</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0005711825797334313</v>
+        <v>0.2626281678676605</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0007181231048889458</v>
+        <v>0.07645769417285919</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001786348060704768</v>
+        <v>0.1548186838626862</v>
       </c>
       <c r="T10" t="n">
-        <v>0.003626599907875061</v>
+        <v>0.1255291849374771</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001181818777695298</v>
+        <v>0.3140664100646973</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0006876266561448574</v>
+        <v>0.000321623869240284</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001010146923363209</v>
+        <v>0.116010956466198</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001778942765668035</v>
+        <v>0.2514166533946991</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0009696286870166659</v>
+        <v>0.2355869859457016</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0005951582570560277</v>
+        <v>0.1775489449501038</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001835453324019909</v>
+        <v>0.03214040026068687</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.001387542579323053</v>
+        <v>0.1686385571956635</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.003756663063541055</v>
+        <v>0.2642158269882202</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0009187291143462062</v>
+        <v>0.128865510225296</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.001353657920844853</v>
+        <v>0.3222390115261078</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.001772540155798197</v>
+        <v>0.007331734523177147</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.003098241984844208</v>
+        <v>0.2759623527526855</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0002338775375392288</v>
+        <v>0.069570392370224</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.001828442327678204</v>
+        <v>0.4652649760246277</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0003032615932170302</v>
+        <v>0.2067746967077255</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0007204525172710419</v>
+        <v>0.05825499445199966</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.002477058907970786</v>
+        <v>0.1280143111944199</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0007155336788855493</v>
+        <v>0.009514071047306061</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.001021503005176783</v>
+        <v>0.0518927201628685</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.001182456966489553</v>
+        <v>0.03463267162442207</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.003322299104183912</v>
+        <v>0.1770053654909134</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.000637305376585573</v>
+        <v>0.1892979592084885</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0005650061648339033</v>
+        <v>0.2253116518259048</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.001624333905056119</v>
+        <v>0.1587597131729126</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.002384277526289225</v>
+        <v>0.1266482323408127</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.01033145189285278</v>
+        <v>0.6928117275238037</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.0006976800505071878</v>
+        <v>0.2291498184204102</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.001135757192969322</v>
+        <v>0.0563616007566452</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.001665673684328794</v>
+        <v>0.3941308856010437</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.007198118604719639</v>
+        <v>0.6143226623535156</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.002126238541677594</v>
+        <v>0.1851827353239059</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.001586250029504299</v>
+        <v>0.007284623570740223</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.0002434069756418467</v>
+        <v>0.05762877687811852</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0006404254818335176</v>
+        <v>0.09765982627868652</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.002162903314456344</v>
+        <v>0.104034498333931</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.003259427845478058</v>
+        <v>0.2006512433290482</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0036181949544698</v>
+        <v>0.254994660615921</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.006300203967839479</v>
+        <v>0.166329562664032</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.005272413603961468</v>
+        <v>0.2519551813602448</v>
       </c>
       <c r="BI10" t="n">
-        <v>6.113993003964424e-05</v>
+        <v>0.2011824548244476</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.001886541023850441</v>
+        <v>0.2208849936723709</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0003915680572390556</v>
+        <v>0.1841703057289124</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0001435359590686858</v>
+        <v>0.1261517852544785</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.000952582573518157</v>
+        <v>0.1657735556364059</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.001101544476114213</v>
+        <v>0.04159773886203766</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.001907182158902287</v>
+        <v>0.1422090977430344</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0002890643081627786</v>
+        <v>0.03947889804840088</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.001076248590834439</v>
+        <v>0.2117427438497543</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.001789130037650466</v>
+        <v>0.2561842203140259</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.003062796546146274</v>
+        <v>0.04394036158919334</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.002111780224367976</v>
+        <v>0.1247566193342209</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.001318699563853443</v>
+        <v>0.0941615104675293</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.005056397989392281</v>
+        <v>0.2339817881584167</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.001363338204100728</v>
+        <v>0.249065101146698</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.001062698662281036</v>
+        <v>0.06862623989582062</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0009896497940644622</v>
+        <v>0.2273445725440979</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.002240251749753952</v>
+        <v>0.5547594428062439</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.001335053355433047</v>
+        <v>0.36001256108284</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.001608462422154844</v>
+        <v>0.08391799032688141</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0005301196360960603</v>
+        <v>0.07286970317363739</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0003564379003364593</v>
+        <v>0.02052287384867668</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.002872977405786514</v>
+        <v>0.233178436756134</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0007753389072604477</v>
+        <v>0.02675061300396919</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.002237807726487517</v>
+        <v>0.009648091159760952</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.001075873733498156</v>
+        <v>0.07795554399490356</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.001388575648888946</v>
+        <v>0.2714265584945679</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0009878200944513083</v>
+        <v>0.06616649031639099</v>
       </c>
       <c r="CK10" t="n">
-        <v>8.56234400998801e-05</v>
+        <v>0.1036203652620316</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0001210129557875916</v>
+        <v>0.01322633028030396</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.001969982404261827</v>
+        <v>0.09339723736047745</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.001159341773018241</v>
+        <v>0.395637035369873</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0002560827415436506</v>
+        <v>0.4107708930969238</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.002328368136659265</v>
+        <v>0.3638462424278259</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.000218512024730444</v>
+        <v>0.1097603514790535</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0004323715111240745</v>
+        <v>0.1888159513473511</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.002396365161985159</v>
+        <v>0.0003912299871444702</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.004114190582185984</v>
+        <v>0.148832768201828</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0005007541622035205</v>
+        <v>0.1609868258237839</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0005448628216981888</v>
+        <v>0.01075325347483158</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.002383040962740779</v>
+        <v>0.2116110771894455</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.001002575154416263</v>
+        <v>0.03194069862365723</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.002636186312884092</v>
+        <v>0.01491475012153387</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0006895130500197411</v>
+        <v>0.02855732291936874</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.00204500206746161</v>
+        <v>0.2661036252975464</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0005804771790280938</v>
+        <v>0.0758284255862236</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0003899814910255373</v>
+        <v>0.03032000362873077</v>
       </c>
       <c r="DD10" t="n">
-        <v>8.033977064769715e-05</v>
+        <v>0.03643057122826576</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.00275598606094718</v>
+        <v>0.2867472767829895</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.004242443013936281</v>
+        <v>0.1763150691986084</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.001156223472207785</v>
+        <v>0.2290240824222565</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0006198934279382229</v>
+        <v>0.1428363919258118</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.001102883601561189</v>
+        <v>0.04685168713331223</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.002364239189773798</v>
+        <v>0.4357346594333649</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.002859942149370909</v>
+        <v>0.1157189235091209</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.003257406875491142</v>
+        <v>0.2445613741874695</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.001572124660015106</v>
+        <v>0.2203749418258667</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.001208395347930491</v>
+        <v>0.018236443400383</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.0005159106804057956</v>
+        <v>0.07295335084199905</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.001349884434603155</v>
+        <v>0.0604102835059166</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.002280129818245769</v>
+        <v>0.1225671246647835</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.001784949097782373</v>
+        <v>0.04772884398698807</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.000147742495755665</v>
+        <v>0.1103354245424271</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.0001429342664778233</v>
+        <v>0.03732757642865181</v>
       </c>
       <c r="DU10" t="n">
-        <v>4.632955824490637e-05</v>
+        <v>0.06049938127398491</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.001318664755672216</v>
+        <v>0.01569095999002457</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0002653893025126308</v>
+        <v>0.06826725602149963</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.002886704867705703</v>
+        <v>0.1658263951539993</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.001306754653342068</v>
+        <v>0.06273589283227921</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.002196326851844788</v>
+        <v>0.01820320636034012</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0001355514395982027</v>
+        <v>0.05822239816188812</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0009465616894885898</v>
+        <v>0.1026809364557266</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0003216548648197204</v>
+        <v>0.05099303275346756</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0008555660606361926</v>
+        <v>0.1360838413238525</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.0001827209198381752</v>
+        <v>0.2784197926521301</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.001245842315256596</v>
+        <v>0.1026863008737564</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.001518979202955961</v>
+        <v>0.08337926119565964</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.0004871932324022055</v>
+        <v>0.1192082166671753</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0009525055065751076</v>
+        <v>0.0587928406894207</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0007822695188224316</v>
+        <v>0.06440366804599762</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.001973370090126991</v>
+        <v>0.2774383127689362</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.002022967441007495</v>
+        <v>0.02907958813011646</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.001644228934310377</v>
+        <v>0.01442110072821379</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.001237958902493119</v>
+        <v>0.01140709407627583</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0006467166822403669</v>
+        <v>0.02667712233960629</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0016601876122877</v>
+        <v>0.1380190998315811</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.001161745516583323</v>
+        <v>0.1716621220111847</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.002078898716717958</v>
+        <v>0.06558199971914291</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.000955152849201113</v>
+        <v>0.163298100233078</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.002060123719274998</v>
+        <v>0.180440679192543</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0004695531388279051</v>
+        <v>0.01503626629710197</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.001500184065662324</v>
+        <v>0.03696984797716141</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.0005182258901186287</v>
+        <v>0.05326458811759949</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0006764329737052321</v>
+        <v>0.004253609105944633</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.002627872629091144</v>
+        <v>0.2220313400030136</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0003114957944490016</v>
+        <v>0.02521445043385029</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.001894685439765453</v>
+        <v>0.02253656834363937</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0005866753635928035</v>
+        <v>0.1102557331323624</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.001818087883293629</v>
+        <v>0.266743004322052</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.000809149001725018</v>
+        <v>0.06285637617111206</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.0001967594143934548</v>
+        <v>0.08474958688020706</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.000282180990325287</v>
+        <v>0.02531023696064949</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.0006477648857980967</v>
+        <v>0.1168024763464928</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.000640824087895453</v>
+        <v>0.1157029271125793</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.001544224680401385</v>
+        <v>0.1438224017620087</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.003742903005331755</v>
+        <v>0.03127871826291084</v>
       </c>
       <c r="FK10" t="n">
-        <v>7.752381497994065e-05</v>
+        <v>0.03391144424676895</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.00179164600558579</v>
+        <v>0.3350701630115509</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.0008458670927211642</v>
+        <v>0.1726277321577072</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.003746494185179472</v>
+        <v>0.2117129415273666</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0009190249838866293</v>
+        <v>0.2986564040184021</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.0005347349215298891</v>
+        <v>0.3029289841651917</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.00467609241604805</v>
+        <v>0.1136175096035004</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.0001444501976948231</v>
+        <v>0.1034058779478073</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.002480356954038143</v>
+        <v>0.1807196736335754</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0009563164203427732</v>
+        <v>0.09453865885734558</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.003388183889910579</v>
+        <v>0.253770500421524</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.000913779076654464</v>
+        <v>0.01434200443327427</v>
       </c>
       <c r="FW10" t="n">
-        <v>8.425413398072124e-06</v>
+        <v>0.3058907985687256</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.003625052515417337</v>
+        <v>0.1005691513419151</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.001851786160841584</v>
+        <v>0.2297640293836594</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0006075685960240662</v>
+        <v>0.0111425593495369</v>
       </c>
       <c r="GA10" t="n">
-        <v>2.171440792153589e-05</v>
+        <v>0.1387906223535538</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0007537802448496222</v>
+        <v>0.009501883760094643</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.005014983005821705</v>
+        <v>0.5469364523887634</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.004158984404057264</v>
+        <v>0.3056453764438629</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.002696500159800053</v>
+        <v>0.01359122432768345</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.00166251219343394</v>
+        <v>0.07524918019771576</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.00109767890535295</v>
+        <v>0.2778302729129791</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.03776775300502777</v>
+        <v>0.1284639537334442</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7492603659629822</v>
+        <v>0.47390016913414</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05363300815224648</v>
+        <v>0.1953251212835312</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3593354523181915</v>
+        <v>0.3316624164581299</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08300642669200897</v>
+        <v>0.02914976142346859</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08537651598453522</v>
+        <v>0.3374386131763458</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04780459403991699</v>
+        <v>0.1770834624767303</v>
       </c>
       <c r="H11" t="n">
-        <v>0.04381764680147171</v>
+        <v>0.155194029211998</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0178690142929554</v>
+        <v>0.0412619486451149</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04262366145849228</v>
+        <v>0.1359759420156479</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6161516308784485</v>
+        <v>0.505560040473938</v>
       </c>
       <c r="L11" t="n">
-        <v>0.006160425022244453</v>
+        <v>0.266332745552063</v>
       </c>
       <c r="M11" t="n">
-        <v>0.372941792011261</v>
+        <v>0.4641927480697632</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1675617694854736</v>
+        <v>0.1036288663744926</v>
       </c>
       <c r="O11" t="n">
-        <v>0.08925234526395798</v>
+        <v>0.2681942284107208</v>
       </c>
       <c r="P11" t="n">
-        <v>0.06698688119649887</v>
+        <v>0.1610720157623291</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.06017487496137619</v>
+        <v>0.07012812793254852</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01305081509053707</v>
+        <v>0.04391848295927048</v>
       </c>
       <c r="S11" t="n">
-        <v>0.05732918530702591</v>
+        <v>0.01544185169041157</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09427081793546677</v>
+        <v>0.01708636246621609</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02827133610844612</v>
+        <v>0.06099487096071243</v>
       </c>
       <c r="V11" t="n">
-        <v>0.03596869856119156</v>
+        <v>0.002938252175226808</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01901865378022194</v>
+        <v>0.03733517602086067</v>
       </c>
       <c r="X11" t="n">
-        <v>0.09385009109973907</v>
+        <v>0.152923971414566</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.05934304744005203</v>
+        <v>0.04215787351131439</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.07105927169322968</v>
+        <v>0.07193373143672943</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.03951521590352058</v>
+        <v>0.08201465010643005</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.08744816482067108</v>
+        <v>0.04665473848581314</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1312735974788666</v>
+        <v>0.1132789105176926</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.02837507613003254</v>
+        <v>0.06671186536550522</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.007803712971508503</v>
+        <v>0.1150285005569458</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.03995047882199287</v>
+        <v>0.005151838064193726</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.022776884958148</v>
+        <v>0.1406734883785248</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.02513732202351093</v>
+        <v>0.07889117300510406</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.01171006169170141</v>
+        <v>0.04201338067650795</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0160887036472559</v>
+        <v>0.0618288666009903</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.02528115920722485</v>
+        <v>0.03953931480646133</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0737881064414978</v>
+        <v>0.1516694724559784</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.005556093994528055</v>
+        <v>0.1076179221272469</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.04689835757017136</v>
+        <v>0.110518604516983</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.07160479575395584</v>
+        <v>0.1100126430392265</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.06053126230835915</v>
+        <v>0.0912979394197464</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0345468744635582</v>
+        <v>0.02590359747409821</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.04446471482515335</v>
+        <v>0.004207873716950417</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.01940457709133625</v>
+        <v>0.03636579960584641</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.08257324993610382</v>
+        <v>0.07199431955814362</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.5243962407112122</v>
+        <v>0.2702506184577942</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.02906031534075737</v>
+        <v>0.1114504709839821</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.1413000971078873</v>
+        <v>0.1781244724988937</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.00679414626210928</v>
+        <v>0.3209075033664703</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.001072421669960022</v>
+        <v>0.1760917007923126</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.05027950182557106</v>
+        <v>0.004378590732812881</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.01696594804525375</v>
+        <v>0.009874516166746616</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.007690169382840395</v>
+        <v>0.08153332024812698</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.05708260089159012</v>
+        <v>0.006795552093535662</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.1347556114196777</v>
+        <v>0.04141674190759659</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.136574998497963</v>
+        <v>0.1559290885925293</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.02301550284028053</v>
+        <v>0.009062843397259712</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.1051015555858612</v>
+        <v>0.2194566279649734</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.08560475707054138</v>
+        <v>0.1127836108207703</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.1180704012513161</v>
+        <v>0.07783134281635284</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.03185101971030235</v>
+        <v>0.04963309690356255</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.01411615591496229</v>
+        <v>0.1345927566289902</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.08159378170967102</v>
+        <v>0.0012369304895401</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.09005334228277206</v>
+        <v>0.01925572007894516</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.07566770911216736</v>
+        <v>0.01300660613924265</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.02708433754742146</v>
+        <v>0.05598945170640945</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.1089161932468414</v>
+        <v>0.01840898767113686</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.08256352692842484</v>
+        <v>0.004918339662253857</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.0598432756960392</v>
+        <v>0.02376473881304264</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.02392518892884254</v>
+        <v>0.006275657564401627</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.02337379939854145</v>
+        <v>0.03465213999152184</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0627584382891655</v>
+        <v>0.04428179189562798</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.2890933752059937</v>
+        <v>0.1758068203926086</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.0707089751958847</v>
+        <v>0.08606882393360138</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.09465343505144119</v>
+        <v>0.1553374826908112</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.07188373059034348</v>
+        <v>0.05104688182473183</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.07115830481052399</v>
+        <v>0.1656345725059509</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.001754135359078646</v>
+        <v>0.06208609044551849</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.02833956107497215</v>
+        <v>0.01158298924565315</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.02991852723062038</v>
+        <v>0.07220966368913651</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.003140280954539776</v>
+        <v>0.002474827691912651</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.1116644814610481</v>
+        <v>0.1686314642429352</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.04012200236320496</v>
+        <v>0.02469667419791222</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.04850831627845764</v>
+        <v>0.1369140297174454</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.02270693704485893</v>
+        <v>0.03231622651219368</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02927756123244762</v>
+        <v>0.0624043270945549</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.0183326993137598</v>
+        <v>0.004334079567342997</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.01614175736904144</v>
+        <v>0.04461095854640007</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.02001583948731422</v>
+        <v>0.006892835255712271</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.1652518510818481</v>
+        <v>0.05304510891437531</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.08152329176664352</v>
+        <v>0.149674266576767</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.01431645639240742</v>
+        <v>0.1619623601436615</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.1192228198051453</v>
+        <v>0.2150482982397079</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.190049484372139</v>
+        <v>0.009691949933767319</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.02783063799142838</v>
+        <v>0.04293861240148544</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.03673886135220528</v>
+        <v>0.03801146149635315</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.09325957298278809</v>
+        <v>0.02044988237321377</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.007481938228011131</v>
+        <v>0.04884756729006767</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0118294470012188</v>
+        <v>0.003199867904186249</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.1140711531043053</v>
+        <v>0.1590482890605927</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.05345211550593376</v>
+        <v>0.03321107476949692</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.06787393242120743</v>
+        <v>0.1405727565288544</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.03633575886487961</v>
+        <v>0.002036492805927992</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.03467593714594841</v>
+        <v>0.06325598806142807</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.01209956221282482</v>
+        <v>0.01166570279747248</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.01524978317320347</v>
+        <v>0.04829664155840874</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.01290502957999706</v>
+        <v>0.01036760956048965</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.09406373649835587</v>
+        <v>0.02157101221382618</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.03949091583490372</v>
+        <v>0.1059299483895302</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.03106659092009068</v>
+        <v>0.01739944145083427</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.242096796631813</v>
+        <v>0.09726756066083908</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.03560671955347061</v>
+        <v>0.1420574188232422</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.02945588156580925</v>
+        <v>0.2938128113746643</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.01240940857678652</v>
+        <v>0.02327790111303329</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.03227972239255905</v>
+        <v>0.2268896698951721</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.02312000840902328</v>
+        <v>0.0353454202413559</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.03872972726821899</v>
+        <v>0.02056099660694599</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.03328788280487061</v>
+        <v>0.1029713302850723</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.05068967491388321</v>
+        <v>0.02832598239183426</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.03951987251639366</v>
+        <v>0.0914471447467804</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.1177041903138161</v>
+        <v>0.03264719992876053</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0311888325959444</v>
+        <v>0.01385707221925259</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.02971467189490795</v>
+        <v>0.07110597193241119</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.02394554764032364</v>
+        <v>0.0805017352104187</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.02240588888525963</v>
+        <v>0.1194334402680397</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.04281150549650192</v>
+        <v>0.01384036615490913</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1569537669420242</v>
+        <v>0.03979060798883438</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.005440502427518368</v>
+        <v>0.08838559687137604</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.06206526234745979</v>
+        <v>0.06509820371866226</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.1137568652629852</v>
+        <v>0.009532238356769085</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.03543988615274429</v>
+        <v>0.1063627004623413</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.02388850413262844</v>
+        <v>0.02163781225681305</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.001572168082930148</v>
+        <v>0.2620433568954468</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.001015871297568083</v>
+        <v>0.2215175628662109</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.009508209303021431</v>
+        <v>0.004348285496234894</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.0672970786690712</v>
+        <v>0.0961533859372139</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.02722632512450218</v>
+        <v>0.07711496204137802</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.073756143450737</v>
+        <v>0.1166786774992943</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.05517832189798355</v>
+        <v>0.01492823846638203</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.03824126720428467</v>
+        <v>0.04943761602044106</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.01414910424500704</v>
+        <v>0.002870170399546623</v>
       </c>
       <c r="EM11" t="n">
-        <v>8.698576129972935e-05</v>
+        <v>0.03342206031084061</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.001532382098957896</v>
+        <v>0.003211274743080139</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.01802309602499008</v>
+        <v>0.01412707380950451</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.09369045495986938</v>
+        <v>0.1383388936519623</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.05060051381587982</v>
+        <v>0.007613269612193108</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.02912797406315804</v>
+        <v>0.07023031264543533</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.03799859434366226</v>
+        <v>0.03582796826958656</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.138533353805542</v>
+        <v>0.02137398347258568</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.019410640001297</v>
+        <v>0.06571748852729797</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.03212764859199524</v>
+        <v>0.04155097529292107</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0106134470552206</v>
+        <v>0.01603602431714535</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.02027257904410362</v>
+        <v>0.006574548780918121</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.1079345643520355</v>
+        <v>0.1875907927751541</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.02268317341804504</v>
+        <v>0.03041663579642773</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.05567420646548271</v>
+        <v>0.1583041399717331</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01919010654091835</v>
+        <v>0.01671232469379902</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0393877848982811</v>
+        <v>0.07319500297307968</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.01691223308444023</v>
+        <v>0.01835470460355282</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.004654907621443272</v>
+        <v>0.06352886557579041</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.02155571617186069</v>
+        <v>0.02263779565691948</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.01284244284033775</v>
+        <v>0.01374285388737917</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.07358406484127045</v>
+        <v>0.0680040568113327</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.004787653684616089</v>
+        <v>0.002338521415367723</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.04680947214365005</v>
+        <v>0.05678774788975716</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.05494653806090355</v>
+        <v>0.09545925259590149</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.008954118005931377</v>
+        <v>0.08624527603387833</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.05730844289064407</v>
+        <v>0.01224742084741592</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.001980917295441031</v>
+        <v>0.003750486299395561</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.01080219820141792</v>
+        <v>0.007393015548586845</v>
       </c>
       <c r="FP11" t="n">
-        <v>3.524436033330858e-05</v>
+        <v>0.03170235455036163</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.149024486541748</v>
+        <v>0.09552782773971558</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.02811199799180031</v>
+        <v>0.1504734754562378</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.06380228698253632</v>
+        <v>0.08593103289604187</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0976397916674614</v>
+        <v>0.08507485687732697</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.005204906687140465</v>
+        <v>0.05323555320501328</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.01249590329825878</v>
+        <v>0.05475638434290886</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.03909606859087944</v>
+        <v>0.06316744536161423</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.03071598708629608</v>
+        <v>0.1722127497196198</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.07296573370695114</v>
+        <v>0.005652912426739931</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0546601414680481</v>
+        <v>0.02794218435883522</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.008183062076568604</v>
+        <v>0.01528938859701157</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.02453206107020378</v>
+        <v>0.1301844120025635</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.05820508673787117</v>
+        <v>0.06294301897287369</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.09201287478208542</v>
+        <v>0.1062634512782097</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.1129232943058014</v>
+        <v>0.128627672791481</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.01454032212495804</v>
+        <v>0.0355960987508297</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.01501580607146025</v>
+        <v>0.07742536813020706</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0182728860527277</v>
+        <v>0.006361397914588451</v>
       </c>
       <c r="B12" t="n">
-        <v>0.005774549208581448</v>
+        <v>0.00939035601913929</v>
       </c>
       <c r="C12" t="n">
-        <v>0.005644812248647213</v>
+        <v>0.00241508730687201</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01357458718121052</v>
+        <v>0.03325881808996201</v>
       </c>
       <c r="E12" t="n">
-        <v>0.007751449476927519</v>
+        <v>0.004762580618262291</v>
       </c>
       <c r="F12" t="n">
-        <v>0.006844499614089727</v>
+        <v>0.00796379242092371</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0001914827735163271</v>
+        <v>0.01051564887166023</v>
       </c>
       <c r="H12" t="n">
-        <v>0.003719883039593697</v>
+        <v>0.009378830902278423</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0002789337886497378</v>
+        <v>0.01181138306856155</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01665468141436577</v>
+        <v>0.004992549307644367</v>
       </c>
       <c r="K12" t="n">
-        <v>0.003337119938805699</v>
+        <v>0.000887486501596868</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005775854457169771</v>
+        <v>0.003297705668956041</v>
       </c>
       <c r="M12" t="n">
-        <v>0.006456281989812851</v>
+        <v>0.04591455310583115</v>
       </c>
       <c r="N12" t="n">
-        <v>0.002836237195879221</v>
+        <v>0.002024966757744551</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0004812517436221242</v>
+        <v>0.01620330661535263</v>
       </c>
       <c r="P12" t="n">
-        <v>0.001328542595729232</v>
+        <v>0.0105825737118721</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.002886898349970579</v>
+        <v>0.001019245595671237</v>
       </c>
       <c r="R12" t="n">
-        <v>0.003598950803279877</v>
+        <v>0.01014509238302708</v>
       </c>
       <c r="S12" t="n">
-        <v>0.002588670235127211</v>
+        <v>0.002130646258592606</v>
       </c>
       <c r="T12" t="n">
-        <v>0.004517531022429466</v>
+        <v>0.002806989476084709</v>
       </c>
       <c r="U12" t="n">
-        <v>0.002068402944132686</v>
+        <v>0.002152054104954004</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0029266148339957</v>
+        <v>0.0009855255484580994</v>
       </c>
       <c r="W12" t="n">
-        <v>0.00500650005415082</v>
+        <v>0.002571952063590288</v>
       </c>
       <c r="X12" t="n">
-        <v>0.001550692948512733</v>
+        <v>0.006308648735284805</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.001821268000639975</v>
+        <v>0.001838514697737992</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.003484454471617937</v>
+        <v>0.002247006865218282</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0003997578751295805</v>
+        <v>0.002861201530322433</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0007202595006674528</v>
+        <v>4.374270793050528e-05</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.007858233526349068</v>
+        <v>0.006435592193156481</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.000891013303771615</v>
+        <v>0.002678235527127981</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.001109056640416384</v>
+        <v>0.001937013119459152</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.004119849298149347</v>
+        <v>0.007184393703937531</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.400262307375669e-05</v>
+        <v>0.006319883279502392</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0004141897370573133</v>
+        <v>0.002049694303423166</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0007796038989908993</v>
+        <v>0.001510168425738811</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.002698596334084868</v>
+        <v>7.69980251789093e-05</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0006328916642814875</v>
+        <v>0.001483729225583375</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.002017507329583168</v>
+        <v>0.002656550845131278</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.001758571481332183</v>
+        <v>0.000649026595056057</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.0005660229362547398</v>
+        <v>0.003680673195049167</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.001938447589054704</v>
+        <v>0.004507961217314005</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.0004385389620438218</v>
+        <v>0.005270741879940033</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.003066947916522622</v>
+        <v>0.00504217715933919</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.002466953359544277</v>
+        <v>0.001219708938151598</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.001019845600239933</v>
+        <v>0.001190233044326305</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.00954581331461668</v>
+        <v>0.0004100042860955</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.003628775244578719</v>
+        <v>0.002549136755988002</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.004706347826868296</v>
+        <v>0.007281134836375713</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.005181188229471445</v>
+        <v>0.01467057317495346</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.005753734614700079</v>
+        <v>0.01202706899493933</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.001659273868426681</v>
+        <v>0.007691469509154558</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.003018165938556194</v>
+        <v>0.002222690731287003</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.003976633306592703</v>
+        <v>0.004076085984706879</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.002457400085404515</v>
+        <v>0.004060434643179178</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.009855590760707855</v>
+        <v>0.006015177816152573</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.01046919915825129</v>
+        <v>0.003100367728620768</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0002566224429756403</v>
+        <v>0.001890122424811125</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.0004186657606624067</v>
+        <v>0.002118805423378944</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.004116630647331476</v>
+        <v>0.007794632576406002</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0004424995859153569</v>
+        <v>0.001041344366967678</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.0008204901241697371</v>
+        <v>0.003121614456176758</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.005167479626834393</v>
+        <v>0.01252776384353638</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.004470926243811846</v>
+        <v>0.008484323509037495</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.001085421303287148</v>
+        <v>0.002139963675290346</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.003047569887712598</v>
+        <v>0.0005395932821556926</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0004893093719147146</v>
+        <v>0.001491094008088112</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.00240284251049161</v>
+        <v>0.005478954873979092</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.003369684796780348</v>
+        <v>0.003133220132440329</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.002211874583736062</v>
+        <v>0.003601137548685074</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.00204667286016047</v>
+        <v>0.001576562877744436</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.002724901307374239</v>
+        <v>0.002337276702746749</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.003303081262856722</v>
+        <v>0.0005601402372121811</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.004176717717200518</v>
+        <v>0.0008077542297542095</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.00133385241497308</v>
+        <v>0.0003497395082376897</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.001872778753750026</v>
+        <v>0.004650528077036142</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.0005030464380979538</v>
+        <v>0.009991421364247799</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.005079019349068403</v>
+        <v>0.004019231535494328</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.001010746811516583</v>
+        <v>0.005784401670098305</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.0008231154642999172</v>
+        <v>0.001877361326478422</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.003171707037836313</v>
+        <v>0.000467916252091527</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.001627771183848381</v>
+        <v>0.00658031739294529</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.003141212509945035</v>
+        <v>0.001650468446314335</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.00239979662001133</v>
+        <v>0.004370223265141249</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.000449319340987131</v>
+        <v>0.002278395229950547</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0003561570192687213</v>
+        <v>0.01113252714276314</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.001651079743169248</v>
+        <v>0.001249929424375296</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.003330252598971128</v>
+        <v>0.003247241722419858</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.0007479229243472219</v>
+        <v>0.0006303544505499303</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.002139716874808073</v>
+        <v>0.004181042313575745</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.0009538184967823327</v>
+        <v>0.003772976575419307</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.004818710032850504</v>
+        <v>0.0009301083628088236</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.002901842352002859</v>
+        <v>0.001504841260612011</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.0006682035746052861</v>
+        <v>0.007752588018774986</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.007221104111522436</v>
+        <v>0.01572542265057564</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.00767927709966898</v>
+        <v>0.003899756353348494</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.002743549412116408</v>
+        <v>0.005018235184252262</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.003007283667102456</v>
+        <v>0.001396040199324489</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.008248372003436089</v>
+        <v>0.008619916625320911</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.001664845971390605</v>
+        <v>0.004203831311315298</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.002435828559100628</v>
+        <v>0.001668808748945594</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.002411536406725645</v>
+        <v>0.002975228242576122</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.0008969549089670181</v>
+        <v>0.002720640739426017</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.001080750720575452</v>
+        <v>0.01227293908596039</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.001613223925232887</v>
+        <v>0.0004900373751297593</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.002908828668296337</v>
+        <v>0.00142657314427197</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.0006341405678540468</v>
+        <v>0.0003550810215529054</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.001533128437586129</v>
+        <v>0.003009979845955968</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.001103093381971121</v>
+        <v>0.002609150717034936</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.00260247103869915</v>
+        <v>0.0009077076683752239</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.006559076253324747</v>
+        <v>0.005696299020200968</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.005853988230228424</v>
+        <v>0.006001606583595276</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.006101997569203377</v>
+        <v>0.005610612221062183</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.004880893044173717</v>
+        <v>0.005220795981585979</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.004723790101706982</v>
+        <v>0.008288167417049408</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.001996012637391686</v>
+        <v>0.00249922089278698</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.008664809167385101</v>
+        <v>0.01228084415197372</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0002285257214680314</v>
+        <v>0.005589371547102928</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.003300564829260111</v>
+        <v>0.0001046726247295737</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0003086546203121543</v>
+        <v>0.00446009449660778</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.001352981198579073</v>
+        <v>0.007259944453835487</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.004114855080842972</v>
+        <v>0.005105865653604269</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.004375857766717672</v>
+        <v>0.002048995811492205</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.001215628231875598</v>
+        <v>0.005290594417601824</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.0008162976009771228</v>
+        <v>0.003768916008993983</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.002605023793876171</v>
+        <v>0.003648296464234591</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.002769694896414876</v>
+        <v>0.00593041954562068</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.003412063699215651</v>
+        <v>0.0004604497808031738</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.001506087253801525</v>
+        <v>0.001275502028875053</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.001963164890184999</v>
+        <v>0.01042121089994907</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.001254698727279902</v>
+        <v>0.002377081662416458</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.0001938675995916128</v>
+        <v>0.0002240376197732985</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.002009647199884057</v>
+        <v>0.008145323023200035</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.002683883300051093</v>
+        <v>0.00292282784357667</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.001513277762569487</v>
+        <v>0.01178097911179066</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.0007174651836976409</v>
+        <v>0.007210039533674717</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.003796650096774101</v>
+        <v>0.006312021519988775</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.004527370911091566</v>
+        <v>0.0007931799627840519</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.003706192132085562</v>
+        <v>0.00123568088747561</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.004582729656249285</v>
+        <v>0.01204122230410576</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.001939702779054642</v>
+        <v>0.001136835315264761</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.001582410302944481</v>
+        <v>0.003410307224839926</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.0007942845113575459</v>
+        <v>0.0006471609231084585</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.001598227070644498</v>
+        <v>0.002493790816515684</v>
       </c>
       <c r="EN12" t="n">
-        <v>5.477866216097027e-05</v>
+        <v>0.00210128934122622</v>
       </c>
       <c r="EO12" t="n">
-        <v>5.439738743007183e-05</v>
+        <v>0.0002686985535547137</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.005042318254709244</v>
+        <v>0.006067093927413225</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.0005117930704727769</v>
+        <v>0.001151511794887483</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0008729359251447022</v>
+        <v>0.01070330757647753</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.001011325977742672</v>
+        <v>0.00230871606618166</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.003525417298078537</v>
+        <v>0.004181251861155033</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.0004202355339657515</v>
+        <v>0.003975591622292995</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.003371583996340632</v>
+        <v>0.003899261821061373</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.005141144618391991</v>
+        <v>0.005541363265365362</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.002628013957291842</v>
+        <v>0.001356863183900714</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.002599604660645127</v>
+        <v>0.003669543191790581</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.001073592226020992</v>
+        <v>0.001348740654066205</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.00107850506901741</v>
+        <v>0.01323166862130165</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.001536184921860695</v>
+        <v>0.001267371699213982</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.002291071228682995</v>
+        <v>0.0004908919217996299</v>
       </c>
       <c r="FD12" t="n">
-        <v>8.646739297546446e-05</v>
+        <v>0.0003768154128920287</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.001947916694916785</v>
+        <v>0.004504384007304907</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.001151419361121953</v>
+        <v>0.002457772381603718</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.001928413286805153</v>
+        <v>0.001462913234718144</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.001798935700207949</v>
+        <v>0.001051581697538495</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.003951140679419041</v>
+        <v>0.002824989147484303</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.001193810137920082</v>
+        <v>0.005370412953197956</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.003877104725688696</v>
+        <v>0.005165404640138149</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.002170321764424443</v>
+        <v>0.009711123071610928</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.00392941664904356</v>
+        <v>6.732135079801083e-05</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.001489676302298903</v>
+        <v>0.002848351141437888</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.002141415607184172</v>
+        <v>0.004397900775074959</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.002658512443304062</v>
+        <v>0.006945844739675522</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.003545660758391023</v>
+        <v>0.007097297813743353</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.005515732802450657</v>
+        <v>0.003806345164775848</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.002707409439608455</v>
+        <v>0.00842740386724472</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.008834459818899632</v>
+        <v>0.005414133425801992</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.003291401779279113</v>
+        <v>0.01136725954711437</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.003048307960852981</v>
+        <v>0.003280334174633026</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.001955892890691757</v>
+        <v>0.01246627047657967</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.0001343294861726463</v>
+        <v>0.002093189628794789</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.00128497276455164</v>
+        <v>0.002758244285359979</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.002291306387633085</v>
+        <v>0.009041157551109791</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.001054439111612737</v>
+        <v>0.008506419137120247</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.001486724358983338</v>
+        <v>0.009137516841292381</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.001804338884539902</v>
+        <v>0.005068088416010141</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.001553412992507219</v>
+        <v>0.00618838332593441</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.005177681799978018</v>
+        <v>0.00757547514513135</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.001901062903925776</v>
+        <v>0.009298871271312237</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.003139721695333719</v>
+        <v>0.00234010280109942</v>
       </c>
     </row>
     <row r="13">
@@ -8396,1140 +8396,1140 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.002605709480121732</v>
+        <v>9.772891473858181e-08</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0142851397395134</v>
+        <v>2.899109290410706e-07</v>
       </c>
       <c r="C15" t="n">
-        <v>0.002458501141518354</v>
+        <v>2.039116608898439e-08</v>
       </c>
       <c r="D15" t="n">
-        <v>0.009851936250925064</v>
+        <v>1.804695557439118e-07</v>
       </c>
       <c r="E15" t="n">
-        <v>0.003741528140380979</v>
+        <v>6.878327951653773e-08</v>
       </c>
       <c r="F15" t="n">
-        <v>0.004910419229418039</v>
+        <v>2.195446029418235e-07</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0009662763332016766</v>
+        <v>3.73619570837036e-08</v>
       </c>
       <c r="H15" t="n">
-        <v>0.000717909075319767</v>
+        <v>1.884495191006863e-07</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001383407856337726</v>
+        <v>7.238989496727299e-08</v>
       </c>
       <c r="J15" t="n">
-        <v>0.005569040775299072</v>
+        <v>2.25075336146574e-09</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01084721367806196</v>
+        <v>2.837435886249295e-07</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001886931131593883</v>
+        <v>1.685427264419559e-08</v>
       </c>
       <c r="M15" t="n">
-        <v>0.008064075373113155</v>
+        <v>2.773745109152514e-07</v>
       </c>
       <c r="N15" t="n">
-        <v>0.00484004057943821</v>
+        <v>1.922066843462744e-07</v>
       </c>
       <c r="O15" t="n">
-        <v>0.006797028239816427</v>
+        <v>2.335086151106225e-07</v>
       </c>
       <c r="P15" t="n">
-        <v>0.002085235901176929</v>
+        <v>2.716821079218334e-08</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.002274186816066504</v>
+        <v>1.326510101762324e-07</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0001771459792507812</v>
+        <v>4.029866929045056e-08</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0009104876662604511</v>
+        <v>2.64567372454394e-08</v>
       </c>
       <c r="T15" t="n">
-        <v>0.001920026144944131</v>
+        <v>6.760338067124394e-08</v>
       </c>
       <c r="U15" t="n">
-        <v>0.002174531808122993</v>
+        <v>9.759433083900149e-08</v>
       </c>
       <c r="V15" t="n">
-        <v>0.001357390312477946</v>
+        <v>1.160262375066168e-08</v>
       </c>
       <c r="W15" t="n">
-        <v>0.001118546584621072</v>
+        <v>6.123829621174082e-08</v>
       </c>
       <c r="X15" t="n">
-        <v>0.001150691765360534</v>
+        <v>4.516302709589581e-08</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.002234593033790588</v>
+        <v>9.139981216321758e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.002124049700796604</v>
+        <v>7.99981592081167e-08</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.002144288271665573</v>
+        <v>5.338915975983127e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.001439095241948962</v>
+        <v>7.245398947475223e-09</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.0008299475302919745</v>
+        <v>5.828761118209513e-08</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.0001600701361894608</v>
+        <v>3.360185907297364e-09</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.001064272364601493</v>
+        <v>9.067365169812547e-08</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0004093321913387626</v>
+        <v>4.928641672563572e-08</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0004318948776926845</v>
+        <v>1.062531751472306e-07</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.0009917865972965956</v>
+        <v>1.750754385909659e-08</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.0003018542483914644</v>
+        <v>1.538531790856723e-07</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.0006795781082473695</v>
+        <v>1.209823263792487e-08</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.001724769012071192</v>
+        <v>3.434796980172905e-08</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.001934876781888306</v>
+        <v>9.410046075686296e-10</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.0009902195306494832</v>
+        <v>1.298049170372906e-07</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.0003357155947014689</v>
+        <v>7.968654358592175e-08</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0004236029053572565</v>
+        <v>5.087974130901785e-08</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.0001354511477984488</v>
+        <v>4.143912946119599e-08</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.0005417864886112511</v>
+        <v>1.418684281162541e-08</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.0003875131951645017</v>
+        <v>2.461893799932113e-08</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.001619729329831898</v>
+        <v>2.572346557982996e-09</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.00046922528417781</v>
+        <v>1.722326814501685e-08</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.009076486341655254</v>
+        <v>2.033945207813304e-07</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.0009832610376179218</v>
+        <v>1.477276612149581e-07</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.003727140603587031</v>
+        <v>1.710397334875324e-08</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.002162228804081678</v>
+        <v>3.195525550836464e-07</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.001755254808813334</v>
+        <v>2.300653108022743e-07</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.0007595574716106057</v>
+        <v>1.648690428623922e-08</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.0004714651149697602</v>
+        <v>3.062408993059762e-09</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.003378759371116757</v>
+        <v>3.879562271436043e-08</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.002195609267801046</v>
+        <v>3.673372006574027e-08</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.003334203036502004</v>
+        <v>1.598090761945059e-07</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.004327886272221804</v>
+        <v>2.243648822286559e-08</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.002011950826272368</v>
+        <v>1.030352478892382e-07</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.003372677601873875</v>
+        <v>2.02815670036216e-07</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.003204653272405267</v>
+        <v>4.930511821044092e-08</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.001054634223692119</v>
+        <v>2.522672737370613e-08</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.002019010484218597</v>
+        <v>1.674768270731875e-07</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.0001546010025776923</v>
+        <v>6.597824153686815e-08</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.0008716014563106</v>
+        <v>1.753125822290258e-08</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.002860189648345113</v>
+        <v>8.0454711337552e-08</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.002914095297455788</v>
+        <v>4.569402634047037e-10</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.0001545262930449098</v>
+        <v>5.355715870791755e-08</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.001168419723398983</v>
+        <v>1.022785767190726e-07</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.265073660761118e-05</v>
+        <v>1.421503004195301e-08</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.0008896882645785809</v>
+        <v>4.617604076884163e-10</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.0007263484876602888</v>
+        <v>7.808309021584137e-08</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.0003598456969484687</v>
+        <v>1.78841883524683e-08</v>
       </c>
       <c r="BU15" t="n">
-        <v>9.568522364133969e-05</v>
+        <v>1.257671922161308e-08</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.004278440959751606</v>
+        <v>9.223666097568639e-08</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.003198005957528949</v>
+        <v>1.171975441138784e-07</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.002396790077909827</v>
+        <v>6.803260177434822e-09</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.001043799216859043</v>
+        <v>5.810891678947883e-08</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.0004153363406658173</v>
+        <v>1.062241139493381e-07</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.001404718845151365</v>
+        <v>8.974642184966797e-08</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.0003741286927834153</v>
+        <v>3.538549009363123e-08</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.002014747587963939</v>
+        <v>4.459537183976181e-09</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.000172811618540436</v>
+        <v>5.055860619052055e-09</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.002083324361592531</v>
+        <v>9.599686734418356e-08</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.00215012882836163</v>
+        <v>1.413648309522841e-09</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.0008659673621878028</v>
+        <v>6.176721001338592e-08</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.0003541135811246932</v>
+        <v>3.177868279635732e-08</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.001249795081093907</v>
+        <v>4.448620671837489e-08</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.0002750717976596206</v>
+        <v>2.465363557746514e-08</v>
       </c>
       <c r="CK15" t="n">
-        <v>3.733890480361879e-06</v>
+        <v>1.528657200822181e-10</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.001327886711806059</v>
+        <v>2.465834292308955e-08</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.001959844259545207</v>
+        <v>7.894534803654096e-08</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.000534023973159492</v>
+        <v>2.192150816426874e-07</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.0004807482182513922</v>
+        <v>1.889976601887611e-07</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.002461627358570695</v>
+        <v>7.353021658218495e-08</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.001215757802128792</v>
+        <v>2.324186532121075e-08</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.001719964435324073</v>
+        <v>2.080841277063428e-08</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.001763964304700494</v>
+        <v>5.080804754697965e-08</v>
       </c>
       <c r="CT15" t="n">
-        <v>9.503385808784515e-05</v>
+        <v>2.710480373480095e-08</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.00113583798520267</v>
+        <v>3.42704034039798e-08</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.843830770871136e-05</v>
+        <v>1.51920467317268e-08</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.001973428064957261</v>
+        <v>8.824085995229325e-08</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.002034334000200033</v>
+        <v>4.844690426608622e-09</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.001597458962351084</v>
+        <v>7.11970429279063e-08</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.0006652268348261714</v>
+        <v>4.592257951685497e-08</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.001334487111307681</v>
+        <v>4.637554695818835e-08</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.000441327691078186</v>
+        <v>2.756962835803733e-08</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.0003151322598569095</v>
+        <v>4.912588114081018e-09</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.0008334211888723075</v>
+        <v>1.283096562332275e-08</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.001909990678541362</v>
+        <v>5.284005766270639e-08</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.0008432173635810614</v>
+        <v>1.766207091691285e-08</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.0003586170496419072</v>
+        <v>2.803217569180561e-08</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.005839151330292225</v>
+        <v>5.460555740910422e-08</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.003205932443961501</v>
+        <v>3.072874577014773e-08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.0007524585817009211</v>
+        <v>1.087411121147852e-07</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.0008860463858582079</v>
+        <v>9.430080050165657e-10</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.0005202338797971606</v>
+        <v>7.135083990306157e-08</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.00129605655092746</v>
+        <v>5.027004590374418e-08</v>
       </c>
       <c r="DN15" t="n">
-        <v>5.949586920905858e-05</v>
+        <v>2.857373004871988e-09</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.0007741040899418294</v>
+        <v>7.308054961185917e-08</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.001451545627787709</v>
+        <v>1.02892112607833e-08</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.0006300400709733367</v>
+        <v>3.320342756296668e-08</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.0002629708033055067</v>
+        <v>4.988688928619922e-08</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.000421001052018255</v>
+        <v>4.044794366109272e-08</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.0004739102441817522</v>
+        <v>6.862238421945221e-08</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.0001702257141005248</v>
+        <v>7.06790714843919e-08</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.001600615913048387</v>
+        <v>1.290892459593351e-08</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.0009590331465005875</v>
+        <v>1.244437886072092e-09</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.001682907342910767</v>
+        <v>2.634015316971272e-08</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.001800391240976751</v>
+        <v>2.848864255611261e-08</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.733966150321066e-05</v>
+        <v>6.229094395848733e-08</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.0005388456047512591</v>
+        <v>5.746737841150207e-08</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.0005028285086154938</v>
+        <v>1.905703506110967e-08</v>
       </c>
       <c r="EC15" t="n">
-        <v>7.364398334175348e-05</v>
+        <v>1.601571497644727e-08</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.0004613978089764714</v>
+        <v>1.003769867224946e-07</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.001308274455368519</v>
+        <v>8.323085154415821e-08</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.0002886468428187072</v>
+        <v>1.687065065425486e-08</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.001509477966465056</v>
+        <v>4.030043143643525e-08</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.001491503906436265</v>
+        <v>4.687773369482784e-08</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.0005708655808120966</v>
+        <v>5.727846996705921e-08</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.0002982899895869195</v>
+        <v>2.907603402491077e-08</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.0008611317025497556</v>
+        <v>6.339793401366478e-08</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.0006967723602429032</v>
+        <v>3.821070038156904e-08</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.0003996615705545992</v>
+        <v>3.063300368921773e-08</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.0003393163497094065</v>
+        <v>1.899458812459898e-09</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.0003717012295965105</v>
+        <v>8.999039735613223e-09</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.0002505999582353979</v>
+        <v>6.154203191499619e-08</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.002120325341820717</v>
+        <v>5.674666425647956e-08</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.0006227099802345037</v>
+        <v>1.071677235842117e-08</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.001475392375141382</v>
+        <v>2.932299381086523e-08</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.0005848665605299175</v>
+        <v>1.859759990452403e-08</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.0009020014549605548</v>
+        <v>1.013884443068491e-08</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.003389917081221938</v>
+        <v>3.764535350114784e-08</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.0005583319580182433</v>
+        <v>3.924226632534555e-08</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.0003222797822672874</v>
+        <v>5.973793903990554e-09</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.001810294925235212</v>
+        <v>1.109929783638108e-07</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.001758353551849723</v>
+        <v>6.603074531597031e-09</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.00117404677439481</v>
+        <v>7.200310392363463e-08</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.0003634677268564701</v>
+        <v>2.39232313958837e-08</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.001138202147558331</v>
+        <v>3.984584751037801e-08</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.0008538754773326218</v>
+        <v>1.112029490712985e-08</v>
       </c>
       <c r="FE15" t="n">
-        <v>1.344462361885235e-05</v>
+        <v>1.156389295431381e-08</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.001571976696141064</v>
+        <v>1.553902340134528e-09</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.001238592900335789</v>
+        <v>1.724287379545331e-09</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.0002264717768412083</v>
+        <v>6.479636738276895e-08</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.001492760726250708</v>
+        <v>3.70183741438268e-08</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.002211856422945857</v>
+        <v>4.494130578791555e-08</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.0001980728266062215</v>
+        <v>3.285568705990727e-09</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.002777001122012734</v>
+        <v>1.70008487287987e-08</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.0002560636785347015</v>
+        <v>1.127456972227492e-08</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.002526889555156231</v>
+        <v>2.895254702650618e-09</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.002197043271735311</v>
+        <v>1.125018300740521e-07</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.0005677177105098963</v>
+        <v>2.747148997173099e-08</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.002565904054790735</v>
+        <v>9.49156202523227e-08</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.0004926141700707376</v>
+        <v>8.117604011204094e-08</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.002065290231257677</v>
+        <v>3.076941368362895e-08</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.00257988041266799</v>
+        <v>2.197436259621099e-07</v>
       </c>
       <c r="FU15" t="n">
-        <v>4.396590520627797e-05</v>
+        <v>7.470155338751283e-08</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.001885910634882748</v>
+        <v>8.463119627322158e-08</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.0018590132240206</v>
+        <v>6.196252400059166e-08</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.001261936617083848</v>
+        <v>3.193369479959074e-08</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.003760033287107944</v>
+        <v>1.611719113725485e-08</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.0008138017146848142</v>
+        <v>5.342555198240007e-08</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.0003111400874331594</v>
+        <v>1.257236164065034e-07</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.0009458366548642516</v>
+        <v>4.575615264457156e-08</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.001942048431374133</v>
+        <v>9.879256879230525e-08</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.0008360095089301467</v>
+        <v>1.394371764718016e-07</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.005025906953960657</v>
+        <v>9.204403284002183e-08</v>
       </c>
       <c r="GF15" t="n">
-        <v>7.488792471121997e-05</v>
+        <v>4.565743338957873e-08</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.0002166843041777611</v>
+        <v>4.438583278698616e-09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.01895345188677311</v>
+        <v>0.004617821890860796</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0321052148938179</v>
+        <v>0.003941913601011038</v>
       </c>
       <c r="C16" t="n">
-        <v>0.008477815426886082</v>
+        <v>0.01826304756104946</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02947145141661167</v>
+        <v>0.005171456374228001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.008650191128253937</v>
+        <v>0.004688153509050608</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1320364773273468</v>
+        <v>0.03016725741326809</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007412616163492203</v>
+        <v>0.00742726307362318</v>
       </c>
       <c r="H16" t="n">
-        <v>0.05177680775523186</v>
+        <v>0.008670836687088013</v>
       </c>
       <c r="I16" t="n">
-        <v>0.03874579817056656</v>
+        <v>0.002606129739433527</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0150388116016984</v>
+        <v>9.767967276275158e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01242013275623322</v>
+        <v>0.002603314584121108</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02810645289719105</v>
+        <v>0.02540714293718338</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0196372214704752</v>
+        <v>0.002455859445035458</v>
       </c>
       <c r="N16" t="n">
-        <v>0.005391037091612816</v>
+        <v>0.009402846917510033</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1160713881254196</v>
+        <v>0.0404362753033638</v>
       </c>
       <c r="P16" t="n">
-        <v>0.003692544996738434</v>
+        <v>0.008754683658480644</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.05081631243228912</v>
+        <v>0.01354382373392582</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01889975927770138</v>
+        <v>0.005318715702742338</v>
       </c>
       <c r="S16" t="n">
-        <v>0.009968951344490051</v>
+        <v>0.004179581068456173</v>
       </c>
       <c r="T16" t="n">
-        <v>0.003526269225403666</v>
+        <v>0.002286729170009494</v>
       </c>
       <c r="U16" t="n">
-        <v>0.01032166182994843</v>
+        <v>0.006852194666862488</v>
       </c>
       <c r="V16" t="n">
-        <v>0.01433112099766731</v>
+        <v>0.002999853808432817</v>
       </c>
       <c r="W16" t="n">
-        <v>0.02310707792639732</v>
+        <v>0.004595302976667881</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02496879175305367</v>
+        <v>0.004337670281529427</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.02250886894762516</v>
+        <v>0.005260657053440809</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0046436982229352</v>
+        <v>0.001620488124899566</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.01232400722801685</v>
+        <v>0.00729804951697588</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.001665713265538216</v>
+        <v>0.01644759625196457</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0302544180303812</v>
+        <v>0.004462012089788914</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.04610158875584602</v>
+        <v>0.003490008879452944</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.02135005965828896</v>
+        <v>0.01165048871189356</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0158371664583683</v>
+        <v>0.00672839442268014</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.000366282882168889</v>
+        <v>0.002226933371275663</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.0147000290453434</v>
+        <v>0.00518439244478941</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.02872258238494396</v>
+        <v>0.006411157082766294</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.02995636127889156</v>
+        <v>0.0006367978057824075</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.006399653851985931</v>
+        <v>0.003687059273943305</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.01549984514713287</v>
+        <v>0.00272225309163332</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.005725248716771603</v>
+        <v>8.517364040017128e-05</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.03156465291976929</v>
+        <v>0.002609054557979107</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.006216450594365597</v>
+        <v>0.004446783568710089</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.01882628723978996</v>
+        <v>0.003668553195893764</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.00270329019986093</v>
+        <v>0.004132539965212345</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.006692688912153244</v>
+        <v>0.0006059331353753805</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.006883783265948296</v>
+        <v>0.0007171774632297456</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.02024094760417938</v>
+        <v>8.272210834547877e-05</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.03037132881581783</v>
+        <v>0.01331994868814945</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.01708530262112617</v>
+        <v>0.004996981471776962</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.05933941900730133</v>
+        <v>0.001994308084249496</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.067549929022789</v>
+        <v>0.0009230736177414656</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.08914267271757126</v>
+        <v>0.02509263157844543</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.02062216214835644</v>
+        <v>0.006500878371298313</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.009403720498085022</v>
+        <v>0.005255708005279303</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.0329512357711792</v>
+        <v>0.001631303457543254</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.001108624623157084</v>
+        <v>0.01164324954152107</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.005860066972672939</v>
+        <v>0.008036126382648945</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.01751957833766937</v>
+        <v>0.01202928740531206</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.02792186476290226</v>
+        <v>0.00589198200032115</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.001390037126839161</v>
+        <v>0.007655310910195112</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.01813196949660778</v>
+        <v>0.00103790033608675</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.01032297592610121</v>
+        <v>0.00104582542553544</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.01301062293350697</v>
+        <v>0.005261088721454144</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.01115261577069759</v>
+        <v>0.01272314786911011</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.01707221567630768</v>
+        <v>0.000746879493817687</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.0414288304746151</v>
+        <v>0.004384124651551247</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.00480446545407176</v>
+        <v>0.00961611233651638</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.00337828416377306</v>
+        <v>0.0003725835122168064</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.009606022387742996</v>
+        <v>0.003282028716057539</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.004103025421500206</v>
+        <v>0.003339574672281742</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.004037346690893173</v>
+        <v>0.0001467070542275906</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.03482639417052269</v>
+        <v>0.0006278890068642795</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.04125414788722992</v>
+        <v>0.007905284874141216</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.009582914412021637</v>
+        <v>0.0009212844888679683</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.00651249848306179</v>
+        <v>0.005457671359181404</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.01421188749372959</v>
+        <v>0.004043552558869123</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.02868510596454144</v>
+        <v>0.005237315781414509</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.04599880799651146</v>
+        <v>0.0006263966206461191</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.05969564616680145</v>
+        <v>0.015275988727808</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.02910887263715267</v>
+        <v>0.001636595232412219</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.005897636525332928</v>
+        <v>0.0009790539043024182</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.006898771040141582</v>
+        <v>0.001590825617313385</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.006171509623527527</v>
+        <v>0.00396928284317255</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.0008121529826894403</v>
+        <v>0.0005605051992461085</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.008778272196650505</v>
+        <v>0.003751961980015039</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.01072007417678833</v>
+        <v>0.001609713304787874</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.006342251319438219</v>
+        <v>0.0008531124331057072</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.03297458216547966</v>
+        <v>0.008165105246007442</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.00493673188611865</v>
+        <v>0.001242579310201108</v>
       </c>
       <c r="CK16" t="n">
-        <v>0.02076698839664459</v>
+        <v>0.002298146486282349</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.00230595818720758</v>
+        <v>0.004251844249665737</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.00814900454133749</v>
+        <v>0.002330158371478319</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.03026887029409409</v>
+        <v>0.002006883267313242</v>
       </c>
       <c r="CO16" t="n">
-        <v>0.006569456309080124</v>
+        <v>0.003960799425840378</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.03614261746406555</v>
+        <v>0.004929505754262209</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.06016184389591217</v>
+        <v>0.006388612557202578</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.03472153842449188</v>
+        <v>0.005572009831666946</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.02330723963677883</v>
+        <v>0.00287680490873754</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.01782544702291489</v>
+        <v>0.006673390977084637</v>
       </c>
       <c r="CU16" t="n">
-        <v>0.0009824011940509081</v>
+        <v>0.0005818025674670935</v>
       </c>
       <c r="CV16" t="n">
-        <v>0.0004932025913149118</v>
+        <v>0.003339767688885331</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.00405204389244318</v>
+        <v>0.0004272782825864851</v>
       </c>
       <c r="CX16" t="n">
-        <v>0.01104308385401964</v>
+        <v>0.003888621460646391</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.003125028219074011</v>
+        <v>0.001262033707462251</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.003987533506006002</v>
+        <v>0.00343541894108057</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.03060627356171608</v>
+        <v>0.008636190555989742</v>
       </c>
       <c r="DB16" t="n">
-        <v>0.007082628551870584</v>
+        <v>0.001093468628823757</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.02474220469594002</v>
+        <v>0.00356531934812665</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.008852912113070488</v>
+        <v>0.003598289098590612</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.005279330536723137</v>
+        <v>0.0007027080282568932</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.0191190242767334</v>
+        <v>0.0008345413953065872</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.0007534129545092583</v>
+        <v>0.005555868148803711</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.01127015240490437</v>
+        <v>0.006037426181137562</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.04986206069588661</v>
+        <v>0.00244171405211091</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.01787982881069183</v>
+        <v>0.006495012436062098</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.004486715421080589</v>
+        <v>0.003537567099556327</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.05388730391860008</v>
+        <v>0.007318818010389805</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.02011008746922016</v>
+        <v>0.006887393537908792</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.01756319776177406</v>
+        <v>0.001798881683498621</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.002196004614233971</v>
+        <v>0.006363242864608765</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.007818087004125118</v>
+        <v>0.0007910036947578192</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.01181304454803467</v>
+        <v>0.0001422556088073179</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.01181171275675297</v>
+        <v>0.01055425684899092</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.03265907615423203</v>
+        <v>0.004080694634467363</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.02116765081882477</v>
+        <v>0.004622507840394974</v>
       </c>
       <c r="DU16" t="n">
-        <v>0.0201275460422039</v>
+        <v>0.001444462104700506</v>
       </c>
       <c r="DV16" t="n">
-        <v>0.01102861016988754</v>
+        <v>0.006770601030439138</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.008805245161056519</v>
+        <v>8.962780702859163e-05</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.0110915144905448</v>
+        <v>0.003783776890486479</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.02315779216587543</v>
+        <v>0.006071720737963915</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.00081458012573421</v>
+        <v>0.002559780608862638</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.01363365259021521</v>
+        <v>0.004852909129112959</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.008775906637310982</v>
+        <v>0.0008979567210189998</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.006286640651524067</v>
+        <v>0.004193194676190615</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.0465480163693428</v>
+        <v>0.006455583497881889</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.004195690155029297</v>
+        <v>0.001136903883889318</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.005532560870051384</v>
+        <v>0.0003638578928075731</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.008454750292003155</v>
+        <v>0.002127270679920912</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.01252828072756529</v>
+        <v>0.000180822127731517</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.01561574637889862</v>
+        <v>0.002820830093696713</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.00904625840485096</v>
+        <v>0.005906482227146626</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.011041727848351</v>
+        <v>0.0006912966491654515</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.00432389322668314</v>
+        <v>0.002326843095943332</v>
       </c>
       <c r="EM16" t="n">
-        <v>0.03043559938669205</v>
+        <v>0.0008832709863781929</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.005649073049426079</v>
+        <v>0.002558175474405289</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.00671009486541152</v>
+        <v>0.004862126894295216</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.002018792554736137</v>
+        <v>0.002400018274784088</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.01624513790011406</v>
+        <v>0.002830062760040164</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.02023032680153847</v>
+        <v>0.007529053371399641</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.002319229068234563</v>
+        <v>0.008980371057987213</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.003539260011166334</v>
+        <v>0.0104278028011322</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.01259259879589081</v>
+        <v>0.008119300007820129</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.03480109199881554</v>
+        <v>0.002880489453673363</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.02209493331611156</v>
+        <v>0.001514579402282834</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.0007234471850097179</v>
+        <v>0.004490718245506287</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.008344382978975773</v>
+        <v>0.000709300977177918</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.004579414147883654</v>
+        <v>0.002660257276147604</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.005242417100816965</v>
+        <v>0.0005924233701080084</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.002639602404087782</v>
+        <v>0.001450680079869926</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.02337086945772171</v>
+        <v>0.008174112066626549</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.003813413204625249</v>
+        <v>0.001448791474103928</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.01833756268024445</v>
+        <v>0.0009301721584051847</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.006284474395215511</v>
+        <v>0.001791317597962916</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.003402062691748142</v>
+        <v>0.002787937177345157</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.009721407666802406</v>
+        <v>0.0008076983503997326</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.00349302077665925</v>
+        <v>0.001159562147222459</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.009415858425199986</v>
+        <v>0.001556102768518031</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.02511117234826088</v>
+        <v>0.004262220114469528</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.01924737729132175</v>
+        <v>0.01310002245008945</v>
       </c>
       <c r="FM16" t="n">
-        <v>0.01073587872087955</v>
+        <v>0.001734125660732388</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.02036020904779434</v>
+        <v>0.00437886081635952</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.02031736262142658</v>
+        <v>0.01154228392988443</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.02648723870515823</v>
+        <v>0.005840273573994637</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.01608001254498959</v>
+        <v>0.004161863587796688</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.0109140407294035</v>
+        <v>0.005945258773863316</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.004053887911140919</v>
+        <v>0.0003022215096279979</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.003785176202654839</v>
+        <v>0.01180791109800339</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.02196623757481575</v>
+        <v>0.003796590259298682</v>
       </c>
       <c r="FV16" t="n">
-        <v>0.0121654262766242</v>
+        <v>0.003354397835209966</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.01205291971564293</v>
+        <v>0.001978107262402773</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.0525706373155117</v>
+        <v>0.009988795034587383</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.0149687584489584</v>
+        <v>0.006198334973305464</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.01594571210443974</v>
+        <v>0.002664900617673993</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.02626677230000496</v>
+        <v>0.001279584132134914</v>
       </c>
       <c r="GB16" t="n">
-        <v>0.01716885715723038</v>
+        <v>0.004970554262399673</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.04367735236883163</v>
+        <v>0.005826286040246487</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.02770794183015823</v>
+        <v>0.001600966323167086</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.01582075655460358</v>
+        <v>0.006236070301383734</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.03000539541244507</v>
+        <v>0.006011806894093752</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.02035508118569851</v>
+        <v>0.0006115582655183971</v>
       </c>
     </row>
     <row r="17">
@@ -10103,571 +10103,571 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5.678310481016524e-05</v>
+        <v>0.1250755935907364</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0002327620313735679</v>
+        <v>0.09682828187942505</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0001557680952828377</v>
+        <v>0.1921534389257431</v>
       </c>
       <c r="D18" t="n">
-        <v>7.91319616837427e-05</v>
+        <v>0.1079773306846619</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00046716452925466</v>
+        <v>0.005942675285041332</v>
       </c>
       <c r="F18" t="n">
-        <v>5.758116458309814e-05</v>
+        <v>0.05007573217153549</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002097549440804869</v>
+        <v>0.06036859005689621</v>
       </c>
       <c r="H18" t="n">
-        <v>7.811890100128949e-05</v>
+        <v>0.004155818372964859</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0001716497208690271</v>
+        <v>0.01799069158732891</v>
       </c>
       <c r="J18" t="n">
-        <v>8.889081072993577e-06</v>
+        <v>0.118332102894783</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0002575239050202072</v>
+        <v>0.04990723729133606</v>
       </c>
       <c r="L18" t="n">
-        <v>4.544675903161988e-05</v>
+        <v>0.1597725301980972</v>
       </c>
       <c r="M18" t="n">
-        <v>8.251840336015448e-05</v>
+        <v>0.1365719437599182</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0002733352012000978</v>
+        <v>0.03129036352038383</v>
       </c>
       <c r="O18" t="n">
-        <v>2.242035407107323e-06</v>
+        <v>0.06108836084604263</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0001948884455487132</v>
+        <v>0.05614157766103745</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.413672235794365e-05</v>
+        <v>0.03748612850904465</v>
       </c>
       <c r="R18" t="n">
-        <v>6.301238317973912e-05</v>
+        <v>0.0381648875772953</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0001042485673679039</v>
+        <v>0.05647371709346771</v>
       </c>
       <c r="T18" t="n">
-        <v>8.023544069146737e-05</v>
+        <v>0.003907382488250732</v>
       </c>
       <c r="U18" t="n">
-        <v>5.969958147034049e-05</v>
+        <v>0.0206933468580246</v>
       </c>
       <c r="V18" t="n">
-        <v>0.000154470995767042</v>
+        <v>0.01847233437001705</v>
       </c>
       <c r="W18" t="n">
-        <v>9.840249549597502e-05</v>
+        <v>0.002952008042484522</v>
       </c>
       <c r="X18" t="n">
-        <v>8.127121691359207e-05</v>
+        <v>0.01593566127121449</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.41508756618714e-07</v>
+        <v>0.03529667481780052</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.985711242014077e-05</v>
+        <v>0.01091943401843309</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.103457493125461e-05</v>
+        <v>0.0006106158252805471</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.548639895394444e-05</v>
+        <v>0.03657212108373642</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.919879105116706e-05</v>
+        <v>0.06883943825960159</v>
       </c>
       <c r="AD18" t="n">
-        <v>6.916551501490176e-05</v>
+        <v>0.06426595896482468</v>
       </c>
       <c r="AE18" t="n">
-        <v>9.022417361848056e-05</v>
+        <v>0.1276385337114334</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.0001545815612189472</v>
+        <v>0.0101176155731082</v>
       </c>
       <c r="AG18" t="n">
-        <v>9.425583994016051e-05</v>
+        <v>0.104385107755661</v>
       </c>
       <c r="AH18" t="n">
-        <v>7.310190994758159e-05</v>
+        <v>0.03521426767110825</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.745955134741962e-05</v>
+        <v>0.1354252547025681</v>
       </c>
       <c r="AJ18" t="n">
-        <v>9.767574374563992e-05</v>
+        <v>0.05865750834345818</v>
       </c>
       <c r="AK18" t="n">
-        <v>5.42394736839924e-05</v>
+        <v>0.0362078845500946</v>
       </c>
       <c r="AL18" t="n">
-        <v>7.407019438687712e-05</v>
+        <v>0.01754979975521564</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.603672353667207e-05</v>
+        <v>0.01085110567510128</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.251232399430592e-05</v>
+        <v>0.003945847041904926</v>
       </c>
       <c r="AO18" t="n">
-        <v>8.675238495925441e-05</v>
+        <v>0.07893695682287216</v>
       </c>
       <c r="AP18" t="n">
-        <v>6.035289698047563e-05</v>
+        <v>0.004003947600722313</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6.516125722555444e-06</v>
+        <v>0.01292813941836357</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.221997990796808e-05</v>
+        <v>0.03344257548451424</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.623237146006431e-06</v>
+        <v>0.0214108619838953</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.414713086793199e-05</v>
+        <v>0.02076396346092224</v>
       </c>
       <c r="AU18" t="n">
-        <v>9.189984120894223e-05</v>
+        <v>0.07818421721458435</v>
       </c>
       <c r="AV18" t="n">
-        <v>7.566899148514494e-05</v>
+        <v>0.1013394594192505</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.964642670936882e-05</v>
+        <v>0.0286445077508688</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.0002740462950896472</v>
+        <v>0.007397480309009552</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.18505504867062e-05</v>
+        <v>0.05837104469537735</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.463528496969957e-05</v>
+        <v>0.03525825962424278</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.227497796207899e-05</v>
+        <v>0.04995292797684669</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.364390280097723e-06</v>
+        <v>0.02725878357887268</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.279130371287465e-05</v>
+        <v>0.08906424790620804</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.416939191287383e-05</v>
+        <v>0.07740624994039536</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.047699151968118e-05</v>
+        <v>0.07910232245922089</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.488874012371525e-05</v>
+        <v>0.02535362541675568</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.0001835263537941501</v>
+        <v>0.01431933883577585</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.983341593993828e-05</v>
+        <v>0.03301484882831573</v>
       </c>
       <c r="BI18" t="n">
-        <v>9.174225124297664e-05</v>
+        <v>0.01395947113633156</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1.780354978109244e-05</v>
+        <v>0.05859231203794479</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.277695501921698e-05</v>
+        <v>0.04894306138157845</v>
       </c>
       <c r="BL18" t="n">
-        <v>7.6622876804322e-05</v>
+        <v>0.04074255004525185</v>
       </c>
       <c r="BM18" t="n">
-        <v>7.363832264672965e-05</v>
+        <v>0.04029865562915802</v>
       </c>
       <c r="BN18" t="n">
-        <v>3.820890015049372e-06</v>
+        <v>0.02343565225601196</v>
       </c>
       <c r="BO18" t="n">
-        <v>6.254764593904838e-05</v>
+        <v>0.02507782727479935</v>
       </c>
       <c r="BP18" t="n">
-        <v>6.350943294819444e-05</v>
+        <v>0.03022281639277935</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.788006117451005e-05</v>
+        <v>0.05019184947013855</v>
       </c>
       <c r="BR18" t="n">
-        <v>6.320963439065963e-05</v>
+        <v>0.038825623691082</v>
       </c>
       <c r="BS18" t="n">
-        <v>3.822815415333025e-05</v>
+        <v>5.322042852640152e-05</v>
       </c>
       <c r="BT18" t="n">
-        <v>4.429116961546242e-05</v>
+        <v>0.03788065910339355</v>
       </c>
       <c r="BU18" t="n">
-        <v>9.766676157596521e-06</v>
+        <v>0.01779766008257866</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.0001800540776457638</v>
+        <v>0.1349040865898132</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.0001058309790096246</v>
+        <v>0.03306606039404869</v>
       </c>
       <c r="BX18" t="n">
-        <v>6.720785313518718e-05</v>
+        <v>0.03672110289335251</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.0001027992693707347</v>
+        <v>0.02951968461275101</v>
       </c>
       <c r="BZ18" t="n">
-        <v>8.697052544448525e-05</v>
+        <v>0.02700651809573174</v>
       </c>
       <c r="CA18" t="n">
-        <v>9.841968130785972e-05</v>
+        <v>0.03951070830225945</v>
       </c>
       <c r="CB18" t="n">
-        <v>2.157308699679561e-05</v>
+        <v>0.01686742343008518</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.266060982947238e-05</v>
+        <v>0.0235856119543314</v>
       </c>
       <c r="CD18" t="n">
-        <v>2.084495281451382e-05</v>
+        <v>0.003091245889663696</v>
       </c>
       <c r="CE18" t="n">
-        <v>3.284265039837919e-05</v>
+        <v>0.04798677563667297</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.836638122971635e-05</v>
+        <v>0.05283074826002121</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.616810888866894e-06</v>
+        <v>0.0106411799788475</v>
       </c>
       <c r="CH18" t="n">
-        <v>7.455710147041827e-05</v>
+        <v>0.0007644629804417491</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.155038717115531e-05</v>
+        <v>0.01343031413853168</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.53589496423956e-06</v>
+        <v>0.009384468197822571</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.759640326781664e-05</v>
+        <v>0.00643823528662324</v>
       </c>
       <c r="CL18" t="n">
-        <v>4.365686254459433e-05</v>
+        <v>4.19258140027523e-05</v>
       </c>
       <c r="CM18" t="n">
-        <v>5.356490873964503e-05</v>
+        <v>0.07200688123703003</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.305440648342483e-05</v>
+        <v>0.0241005253046751</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.433036686648848e-05</v>
+        <v>0.072808638215065</v>
       </c>
       <c r="CP18" t="n">
-        <v>5.710668847314082e-05</v>
+        <v>0.1258582472801208</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.471538093435811e-06</v>
+        <v>0.01952462643384933</v>
       </c>
       <c r="CR18" t="n">
-        <v>3.361913331900723e-05</v>
+        <v>0.03254961594939232</v>
       </c>
       <c r="CS18" t="n">
-        <v>7.106899283826351e-05</v>
+        <v>0.003297752700746059</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.950572343252134e-05</v>
+        <v>0.04772394150495529</v>
       </c>
       <c r="CU18" t="n">
-        <v>8.005494601093233e-05</v>
+        <v>0.05442213639616966</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.757295831339434e-05</v>
+        <v>0.005778949707746506</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.822124431782868e-05</v>
+        <v>0.04777774959802628</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.409766537108226e-05</v>
+        <v>0.06414998322725296</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.612469870655332e-06</v>
+        <v>0.003109576180577278</v>
       </c>
       <c r="CZ18" t="n">
-        <v>5.570448047365062e-05</v>
+        <v>0.01459918078035116</v>
       </c>
       <c r="DA18" t="n">
-        <v>4.072357842233032e-05</v>
+        <v>0.01212086528539658</v>
       </c>
       <c r="DB18" t="n">
-        <v>5.927977326791734e-06</v>
+        <v>0.01175007410347462</v>
       </c>
       <c r="DC18" t="n">
-        <v>8.001680726010818e-06</v>
+        <v>0.01379132829606533</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.443686728132889e-05</v>
+        <v>0.01135111227631569</v>
       </c>
       <c r="DE18" t="n">
-        <v>8.439335942966864e-06</v>
+        <v>0.0299602597951889</v>
       </c>
       <c r="DF18" t="n">
-        <v>2.65686812781496e-05</v>
+        <v>0.04104456305503845</v>
       </c>
       <c r="DG18" t="n">
-        <v>5.54714206373319e-05</v>
+        <v>0.04546012729406357</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.0001259973214473575</v>
+        <v>0.02628602832555771</v>
       </c>
       <c r="DI18" t="n">
-        <v>1.501210408605402e-05</v>
+        <v>0.02899391576647758</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.0001302672171732411</v>
+        <v>0.06679247319698334</v>
       </c>
       <c r="DK18" t="n">
-        <v>0.0001078378045349382</v>
+        <v>0.001741798594594002</v>
       </c>
       <c r="DL18" t="n">
-        <v>4.741735028801486e-05</v>
+        <v>0.02992762252688408</v>
       </c>
       <c r="DM18" t="n">
-        <v>3.271607420174405e-05</v>
+        <v>0.05881234258413315</v>
       </c>
       <c r="DN18" t="n">
-        <v>5.604589387075976e-05</v>
+        <v>0.04780006781220436</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.0001159446983365342</v>
+        <v>0.03195280581712723</v>
       </c>
       <c r="DP18" t="n">
-        <v>4.642009662347846e-05</v>
+        <v>0.01494420692324638</v>
       </c>
       <c r="DQ18" t="n">
-        <v>4.983469989383593e-05</v>
+        <v>0.01334715820848942</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.0001168610469903797</v>
+        <v>0.05638208240270615</v>
       </c>
       <c r="DS18" t="n">
-        <v>3.358992398716509e-05</v>
+        <v>0.01271671615540981</v>
       </c>
       <c r="DT18" t="n">
-        <v>3.006463884958066e-05</v>
+        <v>0.02831155620515347</v>
       </c>
       <c r="DU18" t="n">
-        <v>6.027958443155512e-05</v>
+        <v>0.01056278683245182</v>
       </c>
       <c r="DV18" t="n">
-        <v>3.046384517801926e-05</v>
+        <v>0.00275743193924427</v>
       </c>
       <c r="DW18" t="n">
-        <v>4.201014235150069e-05</v>
+        <v>0.01508470438420773</v>
       </c>
       <c r="DX18" t="n">
-        <v>1.350549700873671e-05</v>
+        <v>0.03795503452420235</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.393224950646982e-05</v>
+        <v>0.09129644185304642</v>
       </c>
       <c r="DZ18" t="n">
-        <v>6.421008947654627e-06</v>
+        <v>0.02040249668061733</v>
       </c>
       <c r="EA18" t="n">
-        <v>4.776952664542478e-06</v>
+        <v>0.02651104331016541</v>
       </c>
       <c r="EB18" t="n">
-        <v>4.103645187569782e-05</v>
+        <v>0.04400843381881714</v>
       </c>
       <c r="EC18" t="n">
-        <v>4.329413786763325e-05</v>
+        <v>0.02241187542676926</v>
       </c>
       <c r="ED18" t="n">
-        <v>1.428727136953967e-05</v>
+        <v>0.02169905230402946</v>
       </c>
       <c r="EE18" t="n">
-        <v>3.140066837659106e-05</v>
+        <v>0.07960809022188187</v>
       </c>
       <c r="EF18" t="n">
-        <v>4.405725121614523e-06</v>
+        <v>0.01114479638636112</v>
       </c>
       <c r="EG18" t="n">
-        <v>2.80666135950014e-05</v>
+        <v>0.01561028137803078</v>
       </c>
       <c r="EH18" t="n">
-        <v>8.723141945665702e-06</v>
+        <v>0.0230532418936491</v>
       </c>
       <c r="EI18" t="n">
-        <v>6.816005770815536e-05</v>
+        <v>0.01964318938553333</v>
       </c>
       <c r="EJ18" t="n">
-        <v>1.663085276959464e-05</v>
+        <v>0.0193626768887043</v>
       </c>
       <c r="EK18" t="n">
-        <v>4.146636001678417e-06</v>
+        <v>0.008357909508049488</v>
       </c>
       <c r="EL18" t="n">
-        <v>2.792989471345209e-05</v>
+        <v>0.01413978356868029</v>
       </c>
       <c r="EM18" t="n">
-        <v>1.071526185114635e-05</v>
+        <v>0.02839124202728271</v>
       </c>
       <c r="EN18" t="n">
-        <v>5.59898471692577e-05</v>
+        <v>0.00216582277789712</v>
       </c>
       <c r="EO18" t="n">
-        <v>3.686821582959965e-05</v>
+        <v>0.03092379495501518</v>
       </c>
       <c r="EP18" t="n">
-        <v>1.939151479746215e-05</v>
+        <v>0.03638804703950882</v>
       </c>
       <c r="EQ18" t="n">
-        <v>3.35574040946085e-05</v>
+        <v>0.006560283713042736</v>
       </c>
       <c r="ER18" t="n">
-        <v>2.277472958667204e-05</v>
+        <v>0.04600374773144722</v>
       </c>
       <c r="ES18" t="n">
-        <v>3.645330070867203e-05</v>
+        <v>0.04825513064861298</v>
       </c>
       <c r="ET18" t="n">
-        <v>8.018781954888254e-05</v>
+        <v>0.08303134888410568</v>
       </c>
       <c r="EU18" t="n">
-        <v>2.657434924913105e-05</v>
+        <v>0.02792618423700333</v>
       </c>
       <c r="EV18" t="n">
-        <v>3.904931509168819e-05</v>
+        <v>0.03209412842988968</v>
       </c>
       <c r="EW18" t="n">
-        <v>2.009783020184841e-05</v>
+        <v>0.006868990138173103</v>
       </c>
       <c r="EX18" t="n">
-        <v>1.730790609144606e-05</v>
+        <v>0.01280428562313318</v>
       </c>
       <c r="EY18" t="n">
-        <v>1.876673195511103e-05</v>
+        <v>0.05266552045941353</v>
       </c>
       <c r="EZ18" t="n">
-        <v>1.890054045361467e-05</v>
+        <v>0.05455620959401131</v>
       </c>
       <c r="FA18" t="n">
-        <v>1.913012965815142e-06</v>
+        <v>0.004785299301147461</v>
       </c>
       <c r="FB18" t="n">
-        <v>5.446635987027548e-05</v>
+        <v>0.00907560158520937</v>
       </c>
       <c r="FC18" t="n">
-        <v>2.693697570066433e-05</v>
+        <v>0.01737483777105808</v>
       </c>
       <c r="FD18" t="n">
-        <v>9.037924428412225e-06</v>
+        <v>0.01176922954618931</v>
       </c>
       <c r="FE18" t="n">
-        <v>5.184581823414192e-06</v>
+        <v>0.02776347100734711</v>
       </c>
       <c r="FF18" t="n">
-        <v>3.580228076316416e-05</v>
+        <v>0.01730343140661716</v>
       </c>
       <c r="FG18" t="n">
-        <v>2.874188430723734e-05</v>
+        <v>0.02153500914573669</v>
       </c>
       <c r="FH18" t="n">
-        <v>3.660606580524473e-06</v>
+        <v>0.03359577059745789</v>
       </c>
       <c r="FI18" t="n">
-        <v>2.332100848434493e-05</v>
+        <v>0.001023197546601295</v>
       </c>
       <c r="FJ18" t="n">
-        <v>4.68464131699875e-05</v>
+        <v>0.06490928679704666</v>
       </c>
       <c r="FK18" t="n">
-        <v>6.003347880323417e-05</v>
+        <v>0.03936450183391571</v>
       </c>
       <c r="FL18" t="n">
-        <v>1.795784919522703e-05</v>
+        <v>0.04368651285767555</v>
       </c>
       <c r="FM18" t="n">
-        <v>6.597202445846051e-05</v>
+        <v>0.02229194343090057</v>
       </c>
       <c r="FN18" t="n">
-        <v>3.07759182760492e-05</v>
+        <v>0.03910407796502113</v>
       </c>
       <c r="FO18" t="n">
-        <v>4.421557605382986e-06</v>
+        <v>0.04097221419215202</v>
       </c>
       <c r="FP18" t="n">
-        <v>9.895137736748438e-06</v>
+        <v>0.04519002884626389</v>
       </c>
       <c r="FQ18" t="n">
-        <v>1.848978354246356e-05</v>
+        <v>0.07669530808925629</v>
       </c>
       <c r="FR18" t="n">
-        <v>1.38437080750009e-05</v>
+        <v>0.08270835876464844</v>
       </c>
       <c r="FS18" t="n">
-        <v>6.114788993727416e-05</v>
+        <v>0.05456975847482681</v>
       </c>
       <c r="FT18" t="n">
-        <v>9.866348409559578e-05</v>
+        <v>0.01661072857677937</v>
       </c>
       <c r="FU18" t="n">
-        <v>1.050369064614642e-06</v>
+        <v>0.1482018977403641</v>
       </c>
       <c r="FV18" t="n">
-        <v>9.687493729870766e-05</v>
+        <v>0.05305064469575882</v>
       </c>
       <c r="FW18" t="n">
-        <v>0.00010805026977323</v>
+        <v>0.02469408884644508</v>
       </c>
       <c r="FX18" t="n">
-        <v>1.592005901329685e-05</v>
+        <v>0.1111667826771736</v>
       </c>
       <c r="FY18" t="n">
-        <v>1.777455327101052e-05</v>
+        <v>0.004504868760704994</v>
       </c>
       <c r="FZ18" t="n">
-        <v>2.146605947928037e-05</v>
+        <v>0.05229564756155014</v>
       </c>
       <c r="GA18" t="n">
-        <v>6.616870814468712e-05</v>
+        <v>0.1063023284077644</v>
       </c>
       <c r="GB18" t="n">
-        <v>6.096088327467442e-07</v>
+        <v>0.004678499419242144</v>
       </c>
       <c r="GC18" t="n">
-        <v>0.0001301907323068008</v>
+        <v>0.09572924673557281</v>
       </c>
       <c r="GD18" t="n">
-        <v>6.180183117976412e-05</v>
+        <v>0.001374930143356323</v>
       </c>
       <c r="GE18" t="n">
-        <v>4.191130574326962e-05</v>
+        <v>0.04682247340679169</v>
       </c>
       <c r="GF18" t="n">
-        <v>4.796597568201832e-05</v>
+        <v>0.07987064123153687</v>
       </c>
       <c r="GG18" t="n">
-        <v>3.031857704627328e-05</v>
+        <v>0.003926386125385761</v>
       </c>
     </row>
   </sheetData>
